--- a/Data/gas_wells/TEMPEST_SGW_2021_Data/2021 Raw Data/GasWell_AirCO2CH4_20210921.xlsx
+++ b/Data/gas_wells/TEMPEST_SGW_2021_Data/2021 Raw Data/GasWell_AirCO2CH4_20210921.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Si-sercfs01\serc\Shared\Biogeochemistry\TEMPEST\Soil (GHG)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/readz_si_edu1/Documents/TEMPEST_real/Data/gas_wells/TEMPEST_SGW_2021_Data/2021 Raw Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BABE352-B7EE-4BAA-9B0D-1D2E6DDDB87D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BABE352-B7EE-4BAA-9B0D-1D2E6DDDB87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19320" yWindow="690" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="STDs and Samples" sheetId="1" r:id="rId1"/>
@@ -617,12 +617,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
@@ -630,44 +629,43 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -682,11 +680,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -702,15 +700,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -723,16 +721,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -793,48 +785,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -863,15 +846,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -909,13 +891,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1403,6 +1385,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1410,7 +1393,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2171,6 +2153,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2178,7 +2161,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2977,6 +2959,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2984,7 +2967,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3744,6 +3726,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3751,7 +3734,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4511,6 +4493,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4518,7 +4501,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5153,6 +5135,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5160,7 +5143,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5915,6 +5897,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5922,7 +5905,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6526,6 +6508,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6533,7 +6516,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7046,6 +7028,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7053,7 +7036,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7936,6 +7918,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7943,7 +7926,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8734,6 +8716,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8741,7 +8724,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9501,6 +9483,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9508,7 +9491,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10268,6 +10250,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10275,7 +10258,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10910,6 +10892,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10917,7 +10900,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11676,6 +11658,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11683,7 +11666,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12287,6 +12269,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -12294,7 +12277,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -22095,14 +22077,14 @@
   <dimension ref="A2:AB66"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="15"/>
-    <col min="6" max="6" width="9.28515625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" style="15" customWidth="1"/>
-    <col min="8" max="10" width="8.7109375" style="15"/>
+    <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="13" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" style="13"/>
+    <col min="6" max="6" width="9.28515625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" style="13" customWidth="1"/>
+    <col min="8" max="10" width="8.7109375" style="13"/>
     <col min="11" max="11" width="25.140625" customWidth="1"/>
     <col min="12" max="12" width="9.5703125" customWidth="1"/>
     <col min="14" max="14" width="9.42578125" customWidth="1"/>
@@ -22111,2720 +22093,2711 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="78"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="H4" s="78"/>
-      <c r="K4" s="1"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="4"/>
-      <c r="H5" s="78"/>
-      <c r="K5" s="1"/>
+      <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:28" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="26" t="s">
+      <c r="J6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="135" t="s">
+      <c r="K6" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="L6" s="76" t="s">
+      <c r="L6" s="72" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="77">
+      <c r="A7" s="73">
         <v>44460</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="17">
         <v>44461</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="18">
         <v>10</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="18">
         <v>1</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="18">
         <v>787</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="18">
         <v>448079</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="18">
         <f>(G7*$AA$14)+$AA$15</f>
         <v>0.48855508351652155</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="19">
         <f t="shared" ref="J7:J38" si="0">(H7*$AA$29)+$AA$30</f>
         <v>3415.3455195636461</v>
       </c>
-      <c r="L7" s="124" t="s">
+      <c r="L7" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="125" t="s">
+      <c r="M7" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="125" t="s">
+      <c r="N7" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="O7" s="126" t="s">
+      <c r="O7" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="P7" s="127" t="s">
+      <c r="P7" s="117" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" s="85">
+      <c r="A8" s="78">
         <v>44460</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>44461</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="14">
         <v>20</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="14">
         <v>2</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="14">
         <v>457</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="14">
         <v>904827</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="14">
         <f t="shared" ref="I8:I66" si="1">(G8*$AA$14)+$AA$15</f>
         <v>-0.15580613099861707</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="15">
         <f t="shared" si="0"/>
         <v>7093.065739137005</v>
       </c>
-      <c r="L8" s="122" t="s">
+      <c r="L8" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="M8" s="53">
+      <c r="M8" s="18">
         <v>7.5</v>
       </c>
-      <c r="N8" s="53">
+      <c r="N8" s="18">
         <v>3702</v>
       </c>
-      <c r="O8" s="54">
+      <c r="O8" s="51">
         <f>AVERAGE(M8:M10)</f>
         <v>7.5</v>
       </c>
-      <c r="P8" s="55">
+      <c r="P8" s="52">
         <f>AVERAGE(N8:N10)</f>
         <v>4250.666666666667</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" s="85">
+      <c r="A9" s="78">
         <v>44460</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <v>44461</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="14">
         <v>35</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="14">
         <v>3</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="14">
         <v>380</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="14">
         <v>1216303</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="14">
         <f t="shared" si="1"/>
         <v>-0.30615708105214945</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="15">
         <f t="shared" si="0"/>
         <v>9601.0604826538511</v>
       </c>
-      <c r="L9" s="123" t="s">
+      <c r="L9" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="M9" s="56">
+      <c r="M9" s="14">
         <v>7.5</v>
       </c>
-      <c r="N9" s="56">
+      <c r="N9" s="14">
         <v>4533</v>
       </c>
-      <c r="O9" s="57"/>
-      <c r="P9" s="58"/>
-      <c r="AB9" s="2"/>
+      <c r="O9" s="53"/>
+      <c r="P9" s="54"/>
+      <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="85">
+      <c r="A10" s="78">
         <v>44460</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>44461</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="14">
         <v>50</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="14">
         <v>4</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="14">
         <v>374</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="14">
         <v>2102267</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="14">
         <f t="shared" si="1"/>
         <v>-0.3178727394978792</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>16734.814142470841</v>
       </c>
-      <c r="L10" s="128" t="s">
+      <c r="L10" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="M10" s="65">
+      <c r="M10" s="61">
         <v>7.5</v>
       </c>
-      <c r="N10" s="59">
+      <c r="N10" s="55">
         <v>4517</v>
       </c>
-      <c r="O10" s="59"/>
-      <c r="P10" s="60"/>
-      <c r="AB10" s="2"/>
+      <c r="O10" s="55"/>
+      <c r="P10" s="56"/>
+      <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" s="86">
+      <c r="A11" s="79">
         <v>44460</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="26">
         <v>44461</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="27">
         <v>10</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="27">
         <v>5</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="27">
         <v>908</v>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="27">
         <v>546324</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="27">
         <f t="shared" si="1"/>
         <v>0.7248208621720722</v>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="28">
         <f t="shared" si="0"/>
         <v>4206.4111027123072</v>
       </c>
-      <c r="L11" s="64" t="s">
+      <c r="L11" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="M11" s="53">
+      <c r="M11" s="18">
         <v>5</v>
       </c>
-      <c r="N11" s="53">
+      <c r="N11" s="18">
         <v>3144</v>
       </c>
-      <c r="O11" s="54">
+      <c r="O11" s="51">
         <f>AVERAGE(M11:M13)</f>
         <v>5</v>
       </c>
-      <c r="P11" s="55">
+      <c r="P11" s="52">
         <f>AVERAGE(N11:N13)</f>
         <v>3207.3333333333335</v>
       </c>
-      <c r="AB11" s="2"/>
+      <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A12" s="87">
+      <c r="A12" s="80">
         <v>44460</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="29">
         <v>44461</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="30">
         <v>20</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="30">
         <v>6</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="30">
         <v>598</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="30">
         <v>2102739</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="30">
         <f t="shared" si="1"/>
         <v>0.11951184247603308</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="31">
         <f t="shared" si="0"/>
         <v>16738.614671304331</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="M12" s="56">
+      <c r="M12" s="14">
         <v>5</v>
       </c>
-      <c r="N12" s="56">
+      <c r="N12" s="14">
         <v>3111</v>
       </c>
-      <c r="O12" s="57"/>
-      <c r="P12" s="58"/>
-      <c r="AB12" s="2"/>
+      <c r="O12" s="53"/>
+      <c r="P12" s="54"/>
+      <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="87">
+      <c r="A13" s="80">
         <v>44460</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="29">
         <v>44461</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="30">
         <v>35</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="30">
         <v>7</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="30">
         <v>557</v>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="30">
         <v>4508934</v>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="30">
         <f t="shared" si="1"/>
         <v>3.9454843096879522E-2</v>
       </c>
-      <c r="J13" s="33">
+      <c r="J13" s="31">
         <f t="shared" si="0"/>
         <v>36113.219494393474</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L13" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="M13" s="65">
+      <c r="M13" s="61">
         <v>5</v>
       </c>
-      <c r="N13" s="65">
+      <c r="N13" s="61">
         <v>3367</v>
       </c>
-      <c r="O13" s="59"/>
-      <c r="P13" s="60"/>
-      <c r="AB13" s="2"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="56"/>
+      <c r="AB13" s="1"/>
     </row>
     <row r="14" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="87">
+      <c r="A14" s="80">
         <v>44460</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="29">
         <v>44461</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="30">
         <v>50</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="30">
         <v>8</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="30">
         <v>383</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="30">
         <v>2866486</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="30">
         <f t="shared" si="1"/>
         <v>-0.30029925182928452</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="31">
         <f t="shared" si="0"/>
         <v>22888.280974251458</v>
       </c>
-      <c r="L14" s="64" t="s">
+      <c r="L14" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="53">
+      <c r="M14" s="18">
         <v>3</v>
       </c>
-      <c r="N14" s="53">
+      <c r="N14" s="18">
         <v>2119</v>
       </c>
-      <c r="O14" s="54">
+      <c r="O14" s="51">
         <f>AVERAGE(M14:M16)</f>
         <v>3</v>
       </c>
-      <c r="P14" s="55">
+      <c r="P14" s="52">
         <f>AVERAGE(N14:N16)</f>
         <v>2195.3333333333335</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Z14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AA14" s="2">
+      <c r="AA14" s="1">
         <f>SLOPE(O8:O22,P8:P22)</f>
         <v>1.9526097409549653E-3</v>
       </c>
-      <c r="AB14" s="2"/>
+      <c r="AB14" s="1"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A15" s="77">
+      <c r="A15" s="73">
         <v>44460</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="17">
         <v>44461</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="18">
         <v>10</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="18">
         <v>9</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="18">
         <v>799</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="18">
         <v>572639</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="18">
         <f t="shared" si="1"/>
         <v>0.51198640040798105</v>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="19">
         <f t="shared" si="0"/>
         <v>4418.2986371472098</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="56">
+      <c r="M15" s="14">
         <v>3</v>
       </c>
-      <c r="N15" s="56">
+      <c r="N15" s="14">
         <v>2154</v>
       </c>
-      <c r="O15" s="57"/>
-      <c r="P15" s="58"/>
-      <c r="Z15" s="3" t="s">
+      <c r="O15" s="53"/>
+      <c r="P15" s="54"/>
+      <c r="Z15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AA15" s="2">
+      <c r="AA15" s="1">
         <f>INTERCEPT(O8:O22,P8:P22)</f>
         <v>-1.0481487826150362</v>
       </c>
-      <c r="AB15" s="2"/>
+      <c r="AB15" s="1"/>
     </row>
     <row r="16" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="85">
+      <c r="A16" s="78">
         <v>44460</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="11">
         <v>44461</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="14">
         <v>20</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="14">
         <v>10</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="14">
         <v>418</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="14">
         <v>1628155</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="14">
         <f t="shared" si="1"/>
         <v>-0.23195791089586071</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="15">
         <f t="shared" si="0"/>
         <v>12917.279552845132</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="M16" s="65">
+      <c r="M16" s="61">
         <v>3</v>
       </c>
-      <c r="N16" s="65">
+      <c r="N16" s="61">
         <v>2313</v>
       </c>
-      <c r="O16" s="59"/>
-      <c r="P16" s="60"/>
-      <c r="Z16" s="3" t="s">
+      <c r="O16" s="55"/>
+      <c r="P16" s="56"/>
+      <c r="Z16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AA16" s="2">
+      <c r="AA16" s="1">
         <f>RSQ(O8:O22,P8:P22)</f>
         <v>0.99370272658207626</v>
       </c>
-      <c r="AB16" s="2"/>
+      <c r="AB16" s="1"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A17" s="85">
+      <c r="A17" s="78">
         <v>44460</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="11">
         <v>44461</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="14">
         <v>35</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="14">
         <v>11</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="14">
         <v>477</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="14">
         <v>1279587</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="14">
         <f t="shared" si="1"/>
         <v>-0.11675393617951779</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="15">
         <f t="shared" si="0"/>
         <v>10110.621217184664</v>
       </c>
-      <c r="L17" s="64" t="s">
+      <c r="L17" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="M17" s="53">
+      <c r="M17" s="18">
         <v>1.5</v>
       </c>
-      <c r="N17" s="53">
+      <c r="N17" s="18">
         <v>1329</v>
       </c>
-      <c r="O17" s="54">
+      <c r="O17" s="51">
         <f>AVERAGE(M17:M19)</f>
         <v>1.5</v>
       </c>
-      <c r="P17" s="55">
+      <c r="P17" s="52">
         <f>AVERAGE(N17:N19)</f>
         <v>1293.6666666666667</v>
       </c>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
-      <c r="AB17" s="2"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="88">
+      <c r="A18" s="81">
         <v>44460</v>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="32">
         <v>44461</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="33">
         <v>50</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="33">
         <v>12</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="33">
         <v>400</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="33">
         <v>1914309</v>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="33">
         <f t="shared" si="1"/>
         <v>-0.26710488623305007</v>
       </c>
-      <c r="J18" s="36">
+      <c r="J18" s="34">
         <f t="shared" si="0"/>
         <v>15221.382366019559</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="M18" s="56">
+      <c r="M18" s="14">
         <v>1.5</v>
       </c>
-      <c r="N18" s="56">
+      <c r="N18" s="14">
         <v>1153</v>
       </c>
-      <c r="O18" s="57"/>
-      <c r="P18" s="58"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
-      <c r="AB18" s="2"/>
+      <c r="O18" s="53"/>
+      <c r="P18" s="54"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="77">
+      <c r="A19" s="73">
         <v>44460</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="17">
         <v>44461</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="18">
         <v>10</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="18">
         <v>13</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="18">
         <v>587</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="18">
         <v>629887</v>
       </c>
-      <c r="I19" s="20">
+      <c r="I19" s="18">
         <f t="shared" si="1"/>
         <v>9.8033135325528376E-2</v>
       </c>
-      <c r="J19" s="21">
+      <c r="J19" s="19">
         <f t="shared" si="0"/>
         <v>4879.2576936294181</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="M19" s="65">
+      <c r="M19" s="61">
         <v>1.5</v>
       </c>
-      <c r="N19" s="65">
+      <c r="N19" s="61">
         <v>1399</v>
       </c>
-      <c r="O19" s="59"/>
-      <c r="P19" s="60"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
+      <c r="O19" s="55"/>
+      <c r="P19" s="56"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A20" s="85">
+      <c r="A20" s="78">
         <v>44460</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="11">
         <v>44461</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="14">
         <v>20</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="14">
         <v>14</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="14">
         <v>388</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="14">
         <v>1401665</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="14">
         <f t="shared" si="1"/>
         <v>-0.29053620312450967</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="15">
         <f t="shared" si="0"/>
         <v>11093.589350520939</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="L20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="M20" s="61">
+      <c r="M20" s="57">
         <v>0.5</v>
       </c>
-      <c r="N20" s="61">
+      <c r="N20" s="57">
         <v>711</v>
       </c>
-      <c r="O20" s="62">
+      <c r="O20" s="58">
         <f>AVERAGE(M20:M22)</f>
         <v>0.5</v>
       </c>
-      <c r="P20" s="63">
+      <c r="P20" s="59">
         <f>AVERAGE(N20:N22)</f>
         <v>699.33333333333337</v>
       </c>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
-      <c r="AB20" s="2"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A21" s="85">
+      <c r="A21" s="78">
         <v>44460</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="11">
         <v>44461</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="14">
         <v>35</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="14">
         <v>15</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="14">
         <v>484</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="14">
         <v>1535244</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="14">
         <f t="shared" si="1"/>
         <v>-0.10308566799283303</v>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="15">
         <f t="shared" si="0"/>
         <v>12169.163166302045</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="L21" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M21" s="56">
+      <c r="M21" s="14">
         <v>0.5</v>
       </c>
-      <c r="N21" s="56">
+      <c r="N21" s="14">
         <v>675</v>
       </c>
-      <c r="O21" s="57"/>
-      <c r="P21" s="58"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="54"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="85">
+      <c r="A22" s="78">
         <v>44460</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="11">
         <v>44461</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="14">
         <v>50</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="14">
         <v>16</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="14">
         <v>375</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="14">
         <v>1632243</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="14">
         <f t="shared" si="1"/>
         <v>-0.31592012975692418</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="15">
         <f t="shared" si="0"/>
         <v>12950.195997487725</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L22" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="M22" s="65">
+      <c r="M22" s="61">
         <v>0.5</v>
       </c>
-      <c r="N22" s="65">
+      <c r="N22" s="61">
         <v>712</v>
       </c>
-      <c r="O22" s="59"/>
-      <c r="P22" s="60"/>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
-      <c r="AB22" s="2"/>
+      <c r="O22" s="55"/>
+      <c r="P22" s="56"/>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A23" s="86">
+      <c r="A23" s="79">
         <v>44460</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="26">
         <v>44461</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="27">
         <v>10</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="27">
         <v>17</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="27">
         <v>803</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="27">
         <v>298800</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="27">
         <f t="shared" si="1"/>
         <v>0.51979683937180088</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="28">
         <f t="shared" si="0"/>
         <v>2213.3558082618092</v>
       </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Z23" s="2"/>
-      <c r="AA23" s="2"/>
-      <c r="AB23" s="2"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1"/>
     </row>
     <row r="24" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="87">
+      <c r="A24" s="80">
         <v>44460</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="29">
         <v>44461</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="30">
         <v>20</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="30">
         <v>18</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="30">
         <v>321</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="30">
         <v>1293507</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="30">
         <f t="shared" si="1"/>
         <v>-0.42136105576849237</v>
       </c>
-      <c r="J24" s="33">
+      <c r="J24" s="31">
         <f t="shared" si="0"/>
         <v>10222.704609901131</v>
       </c>
-      <c r="L24" s="47" t="s">
+      <c r="L24" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="2"/>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="62"/>
+      <c r="P24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
     </row>
     <row r="25" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="87">
+      <c r="A25" s="80">
         <v>44460</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="29">
         <v>44461</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="30">
         <v>35</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="30">
         <v>19</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="30">
         <v>290</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="30">
         <v>2353775</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="30">
         <f t="shared" si="1"/>
         <v>-0.48189195773809623</v>
       </c>
-      <c r="J25" s="33">
+      <c r="J25" s="31">
         <f t="shared" si="0"/>
         <v>18759.948476905709</v>
       </c>
-      <c r="L25" s="48" t="s">
+      <c r="L25" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="M25" s="49" t="s">
+      <c r="M25" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="N25" s="49" t="s">
+      <c r="N25" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="O25" s="50" t="s">
+      <c r="O25" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="P25" s="51" t="s">
+      <c r="P25" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="Z25" s="2"/>
-      <c r="AA25" s="2"/>
-      <c r="AB25" s="2"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
     </row>
     <row r="26" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="89">
+      <c r="A26" s="82">
         <v>44460</v>
       </c>
-      <c r="B26" s="38">
+      <c r="B26" s="36">
         <v>44461</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="D26" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="39">
+      <c r="E26" s="37">
         <v>50</v>
       </c>
-      <c r="F26" s="39">
+      <c r="F26" s="37">
         <v>20</v>
       </c>
-      <c r="G26" s="40">
+      <c r="G26" s="38">
         <v>299</v>
       </c>
-      <c r="H26" s="40">
+      <c r="H26" s="38">
         <v>2306688</v>
       </c>
-      <c r="I26" s="39">
+      <c r="I26" s="37">
         <f t="shared" si="1"/>
         <v>-0.46431847006950155</v>
       </c>
-      <c r="J26" s="41">
+      <c r="J26" s="39">
         <f t="shared" si="0"/>
         <v>18380.805465925801</v>
       </c>
-      <c r="L26" s="122" t="s">
+      <c r="L26" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="M26" s="52">
+      <c r="M26" s="50">
         <v>1375</v>
       </c>
-      <c r="N26" s="52">
+      <c r="N26" s="50">
         <v>178111</v>
       </c>
-      <c r="O26" s="67">
+      <c r="O26" s="63">
         <f>AVERAGE(M26:M28)</f>
         <v>1375</v>
       </c>
-      <c r="P26" s="68">
+      <c r="P26" s="64">
         <f>AVERAGE(N26:N28)</f>
         <v>208441.33333333334</v>
       </c>
-      <c r="Z26" s="2"/>
-      <c r="AA26" s="2"/>
-      <c r="AB26" s="2"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A27" s="77">
+      <c r="A27" s="73">
         <v>44460</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="25">
         <v>44461</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="18">
         <v>10</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="18">
         <v>21</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="20">
         <v>593</v>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="20">
         <v>793348</v>
       </c>
-      <c r="I27" s="20">
+      <c r="I27" s="18">
         <f t="shared" si="1"/>
         <v>0.10974879377125824</v>
       </c>
-      <c r="J27" s="21">
+      <c r="J27" s="19">
         <f t="shared" si="0"/>
         <v>6195.4404132290238</v>
       </c>
-      <c r="L27" s="123" t="s">
+      <c r="L27" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="M27" s="69">
+      <c r="M27" s="65">
         <v>1375</v>
       </c>
-      <c r="N27" s="69">
+      <c r="N27" s="65">
         <v>221219</v>
       </c>
-      <c r="O27" s="70"/>
-      <c r="P27" s="71"/>
-      <c r="Z27" s="2"/>
-      <c r="AA27" s="2"/>
-      <c r="AB27" s="2"/>
+      <c r="O27" s="66"/>
+      <c r="P27" s="67"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
     </row>
     <row r="28" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="85">
+      <c r="A28" s="78">
         <v>44460</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="12">
         <v>44461</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="14">
         <v>20</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="14">
         <v>22</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="16">
         <v>365</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="16">
         <v>1550466</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="14">
         <f t="shared" si="1"/>
         <v>-0.33544622716647388</v>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="15">
         <f t="shared" si="0"/>
         <v>12291.730221182079</v>
       </c>
-      <c r="L28" s="128" t="s">
+      <c r="L28" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="M28" s="72">
+      <c r="M28" s="68">
         <v>1375</v>
       </c>
-      <c r="N28" s="72">
+      <c r="N28" s="68">
         <v>225994</v>
       </c>
-      <c r="O28" s="73"/>
-      <c r="P28" s="74"/>
-      <c r="Z28" s="2"/>
-      <c r="AA28" s="2"/>
-      <c r="AB28" s="2"/>
+      <c r="O28" s="69"/>
+      <c r="P28" s="70"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A29" s="85">
+      <c r="A29" s="78">
         <v>44460</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="12">
         <v>44461</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="14">
         <v>35</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="14">
         <v>23</v>
       </c>
-      <c r="G29" s="18">
+      <c r="G29" s="16">
         <v>527</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H29" s="16">
         <v>1709796</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="14">
         <f t="shared" si="1"/>
         <v>-1.9123449131769554E-2</v>
       </c>
-      <c r="J29" s="17">
+      <c r="J29" s="15">
         <f t="shared" si="0"/>
         <v>13574.650261520786</v>
       </c>
-      <c r="L29" s="64" t="s">
+      <c r="L29" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="M29" s="52">
+      <c r="M29" s="50">
         <v>916.7</v>
       </c>
-      <c r="N29" s="52">
+      <c r="N29" s="50">
         <v>146853</v>
       </c>
-      <c r="O29" s="67">
+      <c r="O29" s="63">
         <f>AVERAGE(M29:M31)</f>
         <v>916.70000000000016</v>
       </c>
-      <c r="P29" s="68">
+      <c r="P29" s="64">
         <f>AVERAGE(N29:N31)</f>
         <v>152923.33333333334</v>
       </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Z29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AA29" s="2">
+      <c r="AA29" s="1">
         <f>SLOPE(O26:O43,P26:P43)</f>
         <v>8.0519678675623294E-3</v>
       </c>
-      <c r="AB29" s="2"/>
+      <c r="AB29" s="1"/>
     </row>
     <row r="30" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="88">
+      <c r="A30" s="81">
         <v>44460</v>
       </c>
-      <c r="B30" s="42">
+      <c r="B30" s="40">
         <v>44461</v>
       </c>
-      <c r="C30" s="43" t="s">
+      <c r="C30" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="35" t="s">
+      <c r="D30" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="33">
         <v>50</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="33">
         <v>24</v>
       </c>
-      <c r="G30" s="43">
+      <c r="G30" s="41">
         <v>366</v>
       </c>
-      <c r="H30" s="43">
+      <c r="H30" s="41">
         <v>3140486</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="33">
         <f t="shared" si="1"/>
         <v>-0.33349361742551886</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="34">
         <f t="shared" si="0"/>
         <v>25094.520169963536</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="L30" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="M30" s="69">
+      <c r="M30" s="65">
         <v>916.7</v>
       </c>
-      <c r="N30" s="69">
+      <c r="N30" s="65">
         <v>146753</v>
       </c>
-      <c r="O30" s="70"/>
-      <c r="P30" s="71"/>
-      <c r="Z30" s="3" t="s">
+      <c r="O30" s="66"/>
+      <c r="P30" s="67"/>
+      <c r="Z30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AA30" s="2">
+      <c r="AA30" s="1">
         <f>INTERCEPT(O26:O43,P26:P43)</f>
         <v>-192.57219056581471</v>
       </c>
-      <c r="AB30" s="2"/>
+      <c r="AB30" s="1"/>
     </row>
     <row r="31" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="77">
+      <c r="A31" s="73">
         <v>44460</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="17">
         <v>44461</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="18">
         <v>10</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="18">
         <v>25</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="18">
         <v>770</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="18">
         <v>848896</v>
       </c>
-      <c r="I31" s="20">
+      <c r="I31" s="18">
         <f t="shared" si="1"/>
         <v>0.45536071792028698</v>
       </c>
-      <c r="J31" s="21">
+      <c r="J31" s="19">
         <f t="shared" si="0"/>
         <v>6642.7111243363761</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="L31" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="M31" s="72">
+      <c r="M31" s="68">
         <v>916.7</v>
       </c>
-      <c r="N31" s="72">
+      <c r="N31" s="68">
         <v>165164</v>
       </c>
-      <c r="O31" s="73"/>
-      <c r="P31" s="74"/>
-      <c r="Z31" s="2" t="s">
+      <c r="O31" s="69"/>
+      <c r="P31" s="70"/>
+      <c r="Z31" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AA31" s="2">
+      <c r="AA31" s="1">
         <f>RSQ(O26:O43,P26:P43)</f>
         <v>0.99835428010997074</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A32" s="85">
+      <c r="A32" s="78">
         <v>44460</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="11">
         <v>44461</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="14">
         <v>20</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="14">
         <v>26</v>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="14">
         <v>468</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="14">
         <v>1734271</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="14">
         <f t="shared" si="1"/>
         <v>-0.13432742384811247</v>
       </c>
-      <c r="J32" s="17">
+      <c r="J32" s="15">
         <f t="shared" si="0"/>
         <v>13771.722175079372</v>
       </c>
-      <c r="L32" s="64" t="s">
+      <c r="L32" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="M32" s="52">
+      <c r="M32" s="50">
         <v>550</v>
       </c>
-      <c r="N32" s="52">
+      <c r="N32" s="50">
         <v>97062</v>
       </c>
-      <c r="O32" s="67">
+      <c r="O32" s="63">
         <f>AVERAGE(M32:M34)</f>
         <v>550</v>
       </c>
-      <c r="P32" s="68">
+      <c r="P32" s="64">
         <f>AVERAGE(N32:N34)</f>
         <v>102639.66666666667</v>
       </c>
-      <c r="Z32" s="2"/>
-      <c r="AA32" s="2"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A33" s="85">
+      <c r="A33" s="78">
         <v>44460</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="11">
         <v>44461</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="14">
         <v>35</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="14">
         <v>27</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="14">
         <v>223</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="14">
         <v>3076190</v>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="14">
         <f t="shared" si="1"/>
         <v>-0.61271681038207892</v>
       </c>
-      <c r="J33" s="17">
+      <c r="J33" s="15">
         <f t="shared" si="0"/>
         <v>24576.810843950749</v>
       </c>
-      <c r="L33" s="9" t="s">
+      <c r="L33" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="M33" s="69">
+      <c r="M33" s="65">
         <v>550</v>
       </c>
-      <c r="N33" s="69">
+      <c r="N33" s="65">
         <v>101176</v>
       </c>
-      <c r="O33" s="70"/>
-      <c r="P33" s="71"/>
-      <c r="Z33" s="2"/>
-      <c r="AA33" s="2"/>
+      <c r="O33" s="66"/>
+      <c r="P33" s="67"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="85">
+      <c r="A34" s="78">
         <v>44460</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="11">
         <v>44461</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="14">
         <v>50</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="14">
         <v>28</v>
       </c>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16">
+      <c r="G34" s="14"/>
+      <c r="H34" s="14">
         <v>4175190</v>
       </c>
-      <c r="I34" s="16"/>
-      <c r="J34" s="17">
+      <c r="I34" s="14"/>
+      <c r="J34" s="15">
         <f t="shared" si="0"/>
         <v>33425.923530401749</v>
       </c>
       <c r="K34" t="s">
         <v>50</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="L34" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="M34" s="72">
+      <c r="M34" s="68">
         <v>550</v>
       </c>
-      <c r="N34" s="72">
+      <c r="N34" s="68">
         <v>109681</v>
       </c>
-      <c r="O34" s="73"/>
-      <c r="P34" s="74"/>
-      <c r="Z34" s="2"/>
-      <c r="AA34" s="2"/>
+      <c r="O34" s="69"/>
+      <c r="P34" s="70"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A35" s="86">
+      <c r="A35" s="79">
         <v>44460</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="26">
         <v>44461</v>
       </c>
-      <c r="C35" s="44" t="s">
+      <c r="C35" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="D35" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E35" s="29">
+      <c r="E35" s="27">
         <v>10</v>
       </c>
-      <c r="F35" s="29">
+      <c r="F35" s="27">
         <v>29</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="27">
         <v>961</v>
       </c>
-      <c r="H35" s="29">
+      <c r="H35" s="27">
         <v>568492</v>
       </c>
-      <c r="I35" s="29">
+      <c r="I35" s="27">
         <f t="shared" si="1"/>
         <v>0.82830917844268548</v>
       </c>
-      <c r="J35" s="30">
+      <c r="J35" s="28">
         <f t="shared" si="0"/>
         <v>4384.9071264004288</v>
       </c>
-      <c r="L35" s="64" t="s">
+      <c r="L35" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="M35" s="52">
+      <c r="M35" s="50">
         <v>275</v>
       </c>
-      <c r="N35" s="52">
+      <c r="N35" s="50">
         <v>59448</v>
       </c>
-      <c r="O35" s="67">
+      <c r="O35" s="63">
         <f>AVERAGE(M35:M37)</f>
         <v>275</v>
       </c>
-      <c r="P35" s="68">
+      <c r="P35" s="64">
         <f>AVERAGE(N35:N37)</f>
         <v>59989</v>
       </c>
-      <c r="Z35" s="2"/>
-      <c r="AA35" s="2"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A36" s="87">
+      <c r="A36" s="80">
         <v>44460</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="29">
         <v>44461</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="C36" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E36" s="32">
+      <c r="E36" s="30">
         <v>20</v>
       </c>
-      <c r="F36" s="32">
+      <c r="F36" s="30">
         <v>30</v>
       </c>
-      <c r="G36" s="32">
+      <c r="G36" s="30">
         <v>489</v>
       </c>
-      <c r="H36" s="32">
+      <c r="H36" s="30">
         <v>1197249</v>
       </c>
-      <c r="I36" s="32">
+      <c r="I36" s="30">
         <f t="shared" si="1"/>
         <v>-9.3322619288058184E-2</v>
       </c>
-      <c r="J36" s="33">
+      <c r="J36" s="31">
         <f t="shared" si="0"/>
         <v>9447.6382869053159</v>
       </c>
-      <c r="L36" s="9" t="s">
+      <c r="L36" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="M36" s="69">
+      <c r="M36" s="65">
         <v>275</v>
       </c>
-      <c r="N36" s="69">
+      <c r="N36" s="65">
         <v>54482</v>
       </c>
-      <c r="O36" s="70"/>
-      <c r="P36" s="71"/>
+      <c r="O36" s="66"/>
+      <c r="P36" s="67"/>
     </row>
     <row r="37" spans="1:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="87">
+      <c r="A37" s="80">
         <v>44460</v>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="29">
         <v>44461</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E37" s="32">
+      <c r="E37" s="30">
         <v>35</v>
       </c>
-      <c r="F37" s="32">
+      <c r="F37" s="30">
         <v>31</v>
       </c>
-      <c r="G37" s="32">
+      <c r="G37" s="30">
         <v>328</v>
       </c>
-      <c r="H37" s="32">
+      <c r="H37" s="30">
         <v>1941069</v>
       </c>
-      <c r="I37" s="32">
+      <c r="I37" s="30">
         <f t="shared" si="1"/>
         <v>-0.4076927875818076</v>
       </c>
-      <c r="J37" s="33">
+      <c r="J37" s="31">
         <f t="shared" si="0"/>
         <v>15436.853026155528</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L37" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="M37" s="72">
+      <c r="M37" s="68">
         <v>275</v>
       </c>
-      <c r="N37" s="72">
+      <c r="N37" s="68">
         <v>66037</v>
       </c>
-      <c r="O37" s="73"/>
-      <c r="P37" s="74"/>
+      <c r="O37" s="69"/>
+      <c r="P37" s="70"/>
     </row>
     <row r="38" spans="1:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="89">
+      <c r="A38" s="82">
         <v>44460</v>
       </c>
-      <c r="B38" s="45">
+      <c r="B38" s="43">
         <v>44461</v>
       </c>
-      <c r="C38" s="40" t="s">
+      <c r="C38" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="D38" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="E38" s="39">
+      <c r="E38" s="37">
         <v>50</v>
       </c>
-      <c r="F38" s="39">
+      <c r="F38" s="37">
         <v>32</v>
       </c>
-      <c r="G38" s="39">
+      <c r="G38" s="37">
         <v>260</v>
       </c>
-      <c r="H38" s="39">
+      <c r="H38" s="37">
         <v>3221858</v>
       </c>
-      <c r="I38" s="39">
+      <c r="I38" s="37">
         <f t="shared" si="1"/>
         <v>-0.5404702499667452</v>
       </c>
-      <c r="J38" s="41">
+      <c r="J38" s="39">
         <f t="shared" si="0"/>
         <v>25749.724899282817</v>
       </c>
-      <c r="L38" s="64" t="s">
+      <c r="L38" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="M38" s="52">
+      <c r="M38" s="50">
         <v>91.7</v>
       </c>
-      <c r="N38" s="52">
+      <c r="N38" s="50">
         <v>28110</v>
       </c>
-      <c r="O38" s="67">
+      <c r="O38" s="63">
         <f>AVERAGE(M38:M40)</f>
         <v>91.7</v>
       </c>
-      <c r="P38" s="68">
+      <c r="P38" s="64">
         <f>AVERAGE(N38:N40)</f>
         <v>30299.333333333332</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A39" s="77">
+      <c r="A39" s="73">
         <v>44460</v>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="17">
         <v>44461</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="18">
         <v>10</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="18">
         <v>33</v>
       </c>
-      <c r="G39" s="20">
+      <c r="G39" s="18">
         <v>741</v>
       </c>
-      <c r="H39" s="20">
+      <c r="H39" s="18">
         <v>1111974</v>
       </c>
-      <c r="I39" s="20">
+      <c r="I39" s="18">
         <f t="shared" si="1"/>
         <v>0.39873503543259314</v>
       </c>
-      <c r="J39" s="21">
+      <c r="J39" s="19">
         <f t="shared" ref="J39:J66" si="2">(H39*$AA$29)+$AA$30</f>
         <v>8761.0067269989377</v>
       </c>
-      <c r="L39" s="9" t="s">
+      <c r="L39" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M39" s="69">
+      <c r="M39" s="65">
         <v>91.7</v>
       </c>
-      <c r="N39" s="69">
+      <c r="N39" s="65">
         <v>31228</v>
       </c>
-      <c r="O39" s="70"/>
-      <c r="P39" s="71"/>
+      <c r="O39" s="66"/>
+      <c r="P39" s="67"/>
     </row>
     <row r="40" spans="1:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="85">
+      <c r="A40" s="78">
         <v>44460</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="11">
         <v>44461</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="14">
         <v>20</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="14">
         <v>34</v>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="14">
         <v>519</v>
       </c>
-      <c r="H40" s="16">
+      <c r="H40" s="14">
         <v>1586666</v>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="14">
         <f t="shared" si="1"/>
         <v>-3.4744327059409219E-2</v>
       </c>
-      <c r="J40" s="17">
+      <c r="J40" s="15">
         <f t="shared" si="2"/>
         <v>12583.211457987836</v>
       </c>
-      <c r="L40" s="11" t="s">
+      <c r="L40" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="M40" s="72">
+      <c r="M40" s="68">
         <v>91.7</v>
       </c>
-      <c r="N40" s="72">
+      <c r="N40" s="68">
         <v>31560</v>
       </c>
-      <c r="O40" s="72"/>
-      <c r="P40" s="129"/>
+      <c r="O40" s="68"/>
+      <c r="P40" s="119"/>
     </row>
     <row r="41" spans="1:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="85">
+      <c r="A41" s="78">
         <v>44460</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="11">
         <v>44461</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="14">
         <v>35</v>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="14">
         <v>35</v>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="14">
         <v>512</v>
       </c>
-      <c r="H41" s="16">
+      <c r="H41" s="14">
         <v>1769483</v>
       </c>
-      <c r="I41" s="16">
+      <c r="I41" s="14">
         <f t="shared" si="1"/>
         <v>-4.8412595246093981E-2</v>
       </c>
-      <c r="J41" s="17">
+      <c r="J41" s="15">
         <f t="shared" si="2"/>
         <v>14055.248067631979</v>
       </c>
-      <c r="L41" s="82" t="s">
+      <c r="L41" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="M41" s="83">
+      <c r="M41" s="76">
         <v>2500</v>
       </c>
-      <c r="N41" s="84">
+      <c r="N41" s="77">
         <v>312334</v>
       </c>
-      <c r="O41" s="84">
+      <c r="O41" s="77">
         <f>AVERAGE(M41:M41)</f>
         <v>2500</v>
       </c>
-      <c r="P41" s="130">
+      <c r="P41" s="120">
         <f>AVERAGE(N41)</f>
         <v>312334</v>
       </c>
     </row>
     <row r="42" spans="1:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="88">
+      <c r="A42" s="81">
         <v>44460</v>
       </c>
-      <c r="B42" s="34">
+      <c r="B42" s="32">
         <v>44461</v>
       </c>
-      <c r="C42" s="43" t="s">
+      <c r="C42" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D42" s="35" t="s">
+      <c r="D42" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="35">
+      <c r="E42" s="33">
         <v>50</v>
       </c>
-      <c r="F42" s="35">
+      <c r="F42" s="33">
         <v>36</v>
       </c>
-      <c r="G42" s="35">
+      <c r="G42" s="33">
         <v>383</v>
       </c>
-      <c r="H42" s="35">
+      <c r="H42" s="33">
         <v>2708883</v>
       </c>
-      <c r="I42" s="35">
+      <c r="I42" s="33">
         <f t="shared" si="1"/>
         <v>-0.30029925182928452</v>
       </c>
-      <c r="J42" s="36">
+      <c r="J42" s="34">
         <f t="shared" si="2"/>
         <v>21619.266682420031</v>
       </c>
-      <c r="L42" s="82" t="s">
+      <c r="L42" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="M42" s="83">
+      <c r="M42" s="76">
         <v>5000</v>
       </c>
-      <c r="N42" s="84">
+      <c r="N42" s="77">
         <v>616504</v>
       </c>
-      <c r="O42" s="84">
+      <c r="O42" s="77">
         <f>AVERAGE(M42:M42)</f>
         <v>5000</v>
       </c>
-      <c r="P42" s="130">
+      <c r="P42" s="120">
         <f t="shared" ref="P42:P43" si="3">AVERAGE(N42)</f>
         <v>616504</v>
       </c>
     </row>
     <row r="43" spans="1:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="77">
+      <c r="A43" s="73">
         <v>44460</v>
       </c>
-      <c r="B43" s="19">
+      <c r="B43" s="17">
         <v>44461</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="18">
         <v>10</v>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="18">
         <v>37</v>
       </c>
-      <c r="G43" s="20">
+      <c r="G43" s="18">
         <v>760</v>
       </c>
-      <c r="H43" s="20">
+      <c r="H43" s="18">
         <v>732768</v>
       </c>
-      <c r="I43" s="20">
+      <c r="I43" s="18">
         <f t="shared" si="1"/>
         <v>0.43583462051073729</v>
       </c>
-      <c r="J43" s="21">
+      <c r="J43" s="19">
         <f t="shared" si="2"/>
         <v>5707.6521998120979</v>
       </c>
-      <c r="L43" s="131" t="s">
+      <c r="L43" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="M43" s="132">
+      <c r="M43" s="122">
         <v>10000</v>
       </c>
-      <c r="N43" s="133">
+      <c r="N43" s="123">
         <v>1280042</v>
       </c>
-      <c r="O43" s="133">
+      <c r="O43" s="123">
         <f>M43</f>
         <v>10000</v>
       </c>
-      <c r="P43" s="134">
+      <c r="P43" s="124">
         <f t="shared" si="3"/>
         <v>1280042</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A44" s="85">
+      <c r="A44" s="78">
         <v>44460</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="11">
         <v>44461</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="14">
         <v>20</v>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="14">
         <v>38</v>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="14">
         <v>548</v>
       </c>
-      <c r="H44" s="16">
+      <c r="H44" s="14">
         <v>1211584</v>
       </c>
-      <c r="I44" s="16">
+      <c r="I44" s="14">
         <f t="shared" si="1"/>
         <v>2.1881355428284843E-2</v>
       </c>
-      <c r="J44" s="17">
+      <c r="J44" s="15">
         <f t="shared" si="2"/>
         <v>9563.0632462868234</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A45" s="85">
+      <c r="A45" s="78">
         <v>44460</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="11">
         <v>44461</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="14">
         <v>35</v>
       </c>
-      <c r="F45" s="16">
+      <c r="F45" s="14">
         <v>39</v>
       </c>
-      <c r="G45" s="16">
+      <c r="G45" s="14">
         <v>399</v>
       </c>
-      <c r="H45" s="16">
+      <c r="H45" s="14">
         <v>1708650</v>
       </c>
-      <c r="I45" s="16">
+      <c r="I45" s="14">
         <f t="shared" si="1"/>
         <v>-0.26905749597400508</v>
       </c>
-      <c r="J45" s="17">
+      <c r="J45" s="15">
         <f t="shared" si="2"/>
         <v>13565.422706344558</v>
       </c>
-      <c r="L45" s="79"/>
-      <c r="M45" s="80"/>
-      <c r="N45" s="81"/>
-      <c r="O45" s="81"/>
-      <c r="P45" s="81"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="74"/>
     </row>
     <row r="46" spans="1:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="85">
+      <c r="A46" s="78">
         <v>44460</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="11">
         <v>44461</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="14">
         <v>50</v>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="14">
         <v>40</v>
       </c>
-      <c r="G46" s="16">
+      <c r="G46" s="14">
         <v>240</v>
       </c>
-      <c r="H46" s="16">
+      <c r="H46" s="14">
         <v>2948519</v>
       </c>
-      <c r="I46" s="16">
+      <c r="I46" s="14">
         <f t="shared" si="1"/>
         <v>-0.57952244478584447</v>
       </c>
-      <c r="J46" s="17">
+      <c r="J46" s="15">
         <f t="shared" si="2"/>
         <v>23548.808054331199</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A47" s="86">
+      <c r="A47" s="79">
         <v>44460</v>
       </c>
-      <c r="B47" s="28">
+      <c r="B47" s="26">
         <v>44461</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D47" s="29" t="s">
+      <c r="D47" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E47" s="29">
+      <c r="E47" s="27">
         <v>10</v>
       </c>
-      <c r="F47" s="29">
+      <c r="F47" s="27">
         <v>41</v>
       </c>
-      <c r="G47" s="29">
+      <c r="G47" s="27">
         <v>888</v>
       </c>
-      <c r="H47" s="29">
+      <c r="H47" s="27">
         <v>445866</v>
       </c>
-      <c r="I47" s="29">
+      <c r="I47" s="27">
         <f t="shared" si="1"/>
         <v>0.68576866735297304</v>
       </c>
-      <c r="J47" s="30">
+      <c r="J47" s="28">
         <f t="shared" si="2"/>
         <v>3397.5265146727311</v>
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A48" s="87">
+      <c r="A48" s="80">
         <v>44460</v>
       </c>
-      <c r="B48" s="31">
+      <c r="B48" s="29">
         <v>44461</v>
       </c>
-      <c r="C48" s="32" t="s">
+      <c r="C48" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D48" s="32" t="s">
+      <c r="D48" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="30">
         <v>20</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="30">
         <v>42</v>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="30">
         <v>460</v>
       </c>
-      <c r="H48" s="32">
+      <c r="H48" s="30">
         <v>1662856</v>
       </c>
-      <c r="I48" s="32">
+      <c r="I48" s="30">
         <f t="shared" si="1"/>
         <v>-0.14994830177575214</v>
       </c>
-      <c r="J48" s="33">
+      <c r="J48" s="31">
         <f t="shared" si="2"/>
         <v>13196.690889817412</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A49" s="87">
+      <c r="A49" s="80">
         <v>44460</v>
       </c>
-      <c r="B49" s="31">
+      <c r="B49" s="29">
         <v>44461</v>
       </c>
-      <c r="C49" s="32" t="s">
+      <c r="C49" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D49" s="32" t="s">
+      <c r="D49" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="E49" s="32">
+      <c r="E49" s="30">
         <v>35</v>
       </c>
-      <c r="F49" s="32">
+      <c r="F49" s="30">
         <v>43</v>
       </c>
-      <c r="G49" s="32">
+      <c r="G49" s="30">
         <v>463</v>
       </c>
-      <c r="H49" s="32">
+      <c r="H49" s="30">
         <v>2166188</v>
       </c>
-      <c r="I49" s="32">
+      <c r="I49" s="30">
         <f t="shared" si="1"/>
         <v>-0.14409047255288732</v>
       </c>
-      <c r="J49" s="33">
+      <c r="J49" s="31">
         <f t="shared" si="2"/>
         <v>17249.503980533293</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="87">
+      <c r="A50" s="80">
         <v>44460</v>
       </c>
-      <c r="B50" s="31">
+      <c r="B50" s="29">
         <v>44461</v>
       </c>
-      <c r="C50" s="32" t="s">
+      <c r="C50" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D50" s="32" t="s">
+      <c r="D50" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="30">
         <v>50</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="30">
         <v>44</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="30">
         <v>304</v>
       </c>
-      <c r="H50" s="32">
+      <c r="H50" s="30">
         <v>4172921</v>
       </c>
-      <c r="I50" s="32">
+      <c r="I50" s="30">
         <f t="shared" si="1"/>
         <v>-0.45455542136472671</v>
       </c>
-      <c r="J50" s="33">
+      <c r="J50" s="31">
         <f t="shared" si="2"/>
         <v>33407.65361531025</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A51" s="77">
+      <c r="A51" s="73">
         <v>44460</v>
       </c>
-      <c r="B51" s="19">
+      <c r="B51" s="17">
         <v>44461</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="C51" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D51" s="20" t="s">
+      <c r="D51" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E51" s="20">
+      <c r="E51" s="18">
         <v>10</v>
       </c>
-      <c r="F51" s="20">
+      <c r="F51" s="18">
         <v>45</v>
       </c>
-      <c r="G51" s="20">
+      <c r="G51" s="18">
         <v>728</v>
       </c>
-      <c r="H51" s="20">
+      <c r="H51" s="18">
         <v>1158652</v>
       </c>
-      <c r="I51" s="20">
+      <c r="I51" s="18">
         <f t="shared" si="1"/>
         <v>0.37335110880017841</v>
       </c>
-      <c r="J51" s="21">
+      <c r="J51" s="19">
         <f t="shared" si="2"/>
         <v>9136.8564831210133</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A52" s="85">
+      <c r="A52" s="78">
         <v>44460</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="11">
         <v>44461</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E52" s="14">
         <v>20</v>
       </c>
-      <c r="F52" s="16">
+      <c r="F52" s="14">
         <v>46</v>
       </c>
-      <c r="G52" s="16">
+      <c r="G52" s="14">
         <v>434</v>
       </c>
-      <c r="H52" s="16">
+      <c r="H52" s="14">
         <v>2435616</v>
       </c>
-      <c r="I52" s="16">
+      <c r="I52" s="14">
         <f t="shared" si="1"/>
         <v>-0.20071615504058127</v>
       </c>
-      <c r="J52" s="17">
+      <c r="J52" s="15">
         <f t="shared" si="2"/>
         <v>19418.929579154876</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A53" s="85">
+      <c r="A53" s="78">
         <v>44460</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="11">
         <v>44461</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="14">
         <v>35</v>
       </c>
-      <c r="F53" s="16">
+      <c r="F53" s="14">
         <v>47</v>
       </c>
-      <c r="G53" s="16">
+      <c r="G53" s="14">
         <v>469</v>
       </c>
-      <c r="H53" s="16">
+      <c r="H53" s="14">
         <v>2851635</v>
       </c>
-      <c r="I53" s="16">
+      <c r="I53" s="14">
         <f t="shared" si="1"/>
         <v>-0.13237481410715746</v>
       </c>
-      <c r="J53" s="17">
+      <c r="J53" s="15">
         <f t="shared" si="2"/>
         <v>22768.70119945029</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="88">
+      <c r="A54" s="81">
         <v>44460</v>
       </c>
-      <c r="B54" s="34">
+      <c r="B54" s="32">
         <v>44461</v>
       </c>
-      <c r="C54" s="35" t="s">
+      <c r="C54" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D54" s="35" t="s">
+      <c r="D54" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E54" s="35">
+      <c r="E54" s="33">
         <v>50</v>
       </c>
-      <c r="F54" s="35">
+      <c r="F54" s="33">
         <v>48</v>
       </c>
-      <c r="G54" s="35">
+      <c r="G54" s="33">
         <v>402</v>
       </c>
-      <c r="H54" s="35">
+      <c r="H54" s="33">
         <v>2472093</v>
       </c>
-      <c r="I54" s="35">
+      <c r="I54" s="33">
         <f t="shared" si="1"/>
         <v>-0.26319966675114015</v>
       </c>
-      <c r="J54" s="36">
+      <c r="J54" s="34">
         <f t="shared" si="2"/>
         <v>19712.641211059949</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A55" s="77">
+      <c r="A55" s="73">
         <v>44460</v>
       </c>
-      <c r="B55" s="19">
+      <c r="B55" s="17">
         <v>44461</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="C55" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D55" s="20" t="s">
+      <c r="D55" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E55" s="20">
+      <c r="E55" s="18">
         <v>10</v>
       </c>
-      <c r="F55" s="20">
+      <c r="F55" s="18">
         <v>49</v>
       </c>
-      <c r="G55" s="20">
+      <c r="G55" s="18">
         <v>688</v>
       </c>
-      <c r="H55" s="20">
+      <c r="H55" s="18">
         <v>1092410</v>
       </c>
-      <c r="I55" s="20">
+      <c r="I55" s="18">
         <f t="shared" si="1"/>
         <v>0.29524671916197986</v>
       </c>
-      <c r="J55" s="21">
+      <c r="J55" s="19">
         <f t="shared" si="2"/>
         <v>8603.4780276379497</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A56" s="85">
+      <c r="A56" s="78">
         <v>44460</v>
       </c>
-      <c r="B56" s="13">
+      <c r="B56" s="11">
         <v>44461</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D56" s="16" t="s">
+      <c r="D56" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E56" s="16">
+      <c r="E56" s="14">
         <v>20</v>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="14">
         <v>50</v>
       </c>
-      <c r="G56" s="16">
+      <c r="G56" s="14">
         <v>406</v>
       </c>
-      <c r="H56" s="16">
+      <c r="H56" s="14">
         <v>2945042</v>
       </c>
-      <c r="I56" s="16">
+      <c r="I56" s="14">
         <f t="shared" si="1"/>
         <v>-0.25538922778732032</v>
       </c>
-      <c r="J56" s="17">
+      <c r="J56" s="15">
         <f t="shared" si="2"/>
         <v>23520.811362055683</v>
       </c>
-      <c r="N56" s="75"/>
-      <c r="O56" s="75"/>
-      <c r="P56" s="75"/>
-      <c r="Q56" s="75"/>
+      <c r="N56" s="71"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="71"/>
+      <c r="Q56" s="71"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A57" s="85">
+      <c r="A57" s="78">
         <v>44460</v>
       </c>
-      <c r="B57" s="13">
+      <c r="B57" s="11">
         <v>44461</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D57" s="16" t="s">
+      <c r="D57" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="16">
+      <c r="E57" s="14">
         <v>35</v>
       </c>
-      <c r="F57" s="16">
+      <c r="F57" s="14">
         <v>51</v>
       </c>
-      <c r="G57" s="16">
+      <c r="G57" s="14">
         <v>592</v>
       </c>
-      <c r="H57" s="16">
+      <c r="H57" s="14">
         <v>2237653</v>
       </c>
-      <c r="I57" s="16">
+      <c r="I57" s="14">
         <f t="shared" si="1"/>
         <v>0.10779618403030322</v>
       </c>
-      <c r="J57" s="17">
+      <c r="J57" s="15">
         <f t="shared" si="2"/>
         <v>17824.937864188636</v>
       </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" s="2"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
     </row>
     <row r="58" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="88">
+      <c r="A58" s="81">
         <v>44460</v>
       </c>
-      <c r="B58" s="34">
+      <c r="B58" s="32">
         <v>44461</v>
       </c>
-      <c r="C58" s="35" t="s">
+      <c r="C58" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D58" s="35" t="s">
+      <c r="D58" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E58" s="35">
+      <c r="E58" s="33">
         <v>50</v>
       </c>
-      <c r="F58" s="35">
+      <c r="F58" s="33">
         <v>52</v>
       </c>
-      <c r="G58" s="35">
+      <c r="G58" s="33">
         <v>421</v>
       </c>
-      <c r="H58" s="35">
+      <c r="H58" s="33">
         <v>4500697</v>
       </c>
-      <c r="I58" s="35">
+      <c r="I58" s="33">
         <f t="shared" si="1"/>
         <v>-0.22610008167299578</v>
       </c>
-      <c r="J58" s="36">
+      <c r="J58" s="34">
         <f t="shared" si="2"/>
         <v>36046.895435068356</v>
       </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A59" s="86">
+      <c r="A59" s="79">
         <v>44460</v>
       </c>
-      <c r="B59" s="28">
+      <c r="B59" s="26">
         <v>44461</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D59" s="29" t="s">
+      <c r="D59" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E59" s="29">
+      <c r="E59" s="27">
         <v>10</v>
       </c>
-      <c r="F59" s="29">
+      <c r="F59" s="27">
         <v>53</v>
       </c>
-      <c r="G59" s="29">
+      <c r="G59" s="27">
         <v>768</v>
       </c>
-      <c r="H59" s="29">
+      <c r="H59" s="27">
         <v>629026</v>
       </c>
-      <c r="I59" s="29">
+      <c r="I59" s="27">
         <f t="shared" si="1"/>
         <v>0.45145549843837718</v>
       </c>
-      <c r="J59" s="30">
+      <c r="J59" s="28">
         <f t="shared" si="2"/>
         <v>4872.3249492954474</v>
       </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A60" s="87">
+      <c r="A60" s="80">
         <v>44460</v>
       </c>
-      <c r="B60" s="31">
+      <c r="B60" s="29">
         <v>44461</v>
       </c>
-      <c r="C60" s="32" t="s">
+      <c r="C60" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D60" s="32" t="s">
+      <c r="D60" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E60" s="32">
+      <c r="E60" s="30">
         <v>20</v>
       </c>
-      <c r="F60" s="32">
+      <c r="F60" s="30">
         <v>54</v>
       </c>
-      <c r="G60" s="32">
+      <c r="G60" s="30">
         <v>383</v>
       </c>
-      <c r="H60" s="32">
+      <c r="H60" s="30">
         <v>1487647</v>
       </c>
-      <c r="I60" s="32">
+      <c r="I60" s="30">
         <f t="shared" si="1"/>
         <v>-0.30029925182928452</v>
       </c>
-      <c r="J60" s="33">
+      <c r="J60" s="31">
         <f t="shared" si="2"/>
         <v>11785.913651709681</v>
       </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" s="2"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A61" s="87">
+      <c r="A61" s="80">
         <v>44460</v>
       </c>
-      <c r="B61" s="31">
+      <c r="B61" s="29">
         <v>44461</v>
       </c>
-      <c r="C61" s="32" t="s">
+      <c r="C61" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D61" s="32" t="s">
+      <c r="D61" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E61" s="32">
+      <c r="E61" s="30">
         <v>35</v>
       </c>
-      <c r="F61" s="32">
+      <c r="F61" s="30">
         <v>55</v>
       </c>
-      <c r="G61" s="32">
+      <c r="G61" s="30">
         <v>344</v>
       </c>
-      <c r="H61" s="32">
+      <c r="H61" s="30">
         <v>1907398</v>
       </c>
-      <c r="I61" s="32">
+      <c r="I61" s="30">
         <f t="shared" si="1"/>
         <v>-0.37645103172652816</v>
       </c>
-      <c r="J61" s="33">
+      <c r="J61" s="31">
         <f t="shared" si="2"/>
         <v>15165.735216086836</v>
       </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" s="2"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
     </row>
     <row r="62" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="89">
+      <c r="A62" s="82">
         <v>44460</v>
       </c>
-      <c r="B62" s="45">
+      <c r="B62" s="43">
         <v>44461</v>
       </c>
-      <c r="C62" s="39" t="s">
+      <c r="C62" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="D62" s="39" t="s">
+      <c r="D62" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="E62" s="39">
+      <c r="E62" s="37">
         <v>50</v>
       </c>
-      <c r="F62" s="39">
+      <c r="F62" s="37">
         <v>56</v>
       </c>
-      <c r="G62" s="39">
+      <c r="G62" s="37">
         <v>369</v>
       </c>
-      <c r="H62" s="39">
+      <c r="H62" s="37">
         <v>2452548</v>
       </c>
-      <c r="I62" s="39">
+      <c r="I62" s="37">
         <f t="shared" si="1"/>
         <v>-0.32763578820265404</v>
       </c>
-      <c r="J62" s="41">
+      <c r="J62" s="39">
         <f t="shared" si="2"/>
         <v>19555.265499088444</v>
       </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" s="2"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A63" s="77">
+      <c r="A63" s="73">
         <v>44460</v>
       </c>
-      <c r="B63" s="19">
+      <c r="B63" s="17">
         <v>44461</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D63" s="20" t="s">
+      <c r="D63" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E63" s="20">
+      <c r="E63" s="18">
         <v>10</v>
       </c>
-      <c r="F63" s="20">
+      <c r="F63" s="18">
         <v>57</v>
       </c>
-      <c r="G63" s="20">
+      <c r="G63" s="18">
         <v>646</v>
       </c>
-      <c r="H63" s="20">
+      <c r="H63" s="18">
         <v>1417274</v>
       </c>
-      <c r="I63" s="20">
+      <c r="I63" s="18">
         <f t="shared" si="1"/>
         <v>0.21323711004187129</v>
       </c>
-      <c r="J63" s="21">
+      <c r="J63" s="19">
         <f t="shared" si="2"/>
         <v>11219.272516965717</v>
       </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" s="2"/>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A64" s="85">
+      <c r="A64" s="78">
         <v>44460</v>
       </c>
-      <c r="B64" s="13">
+      <c r="B64" s="11">
         <v>44461</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C64" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D64" s="16" t="s">
+      <c r="D64" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E64" s="16">
+      <c r="E64" s="14">
         <v>20</v>
       </c>
-      <c r="F64" s="16">
+      <c r="F64" s="14">
         <v>58</v>
       </c>
-      <c r="G64" s="16">
+      <c r="G64" s="14">
         <v>379</v>
       </c>
-      <c r="H64" s="16">
+      <c r="H64" s="14">
         <v>2298225</v>
       </c>
-      <c r="I64" s="16">
+      <c r="I64" s="14">
         <f t="shared" si="1"/>
         <v>-0.30810969079310435</v>
       </c>
-      <c r="J64" s="17">
+      <c r="J64" s="15">
         <f t="shared" si="2"/>
         <v>18312.661661862621</v>
       </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" s="2"/>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="1"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" s="85">
+      <c r="A65" s="78">
         <v>44460</v>
       </c>
-      <c r="B65" s="13">
+      <c r="B65" s="11">
         <v>44461</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="C65" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D65" s="16" t="s">
+      <c r="D65" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E65" s="16">
+      <c r="E65" s="14">
         <v>35</v>
       </c>
-      <c r="F65" s="16">
+      <c r="F65" s="14">
         <v>59</v>
       </c>
-      <c r="G65" s="16">
+      <c r="G65" s="14">
         <v>323</v>
       </c>
-      <c r="H65" s="16">
+      <c r="H65" s="14">
         <v>4123639</v>
       </c>
-      <c r="I65" s="16">
+      <c r="I65" s="14">
         <f t="shared" si="1"/>
         <v>-0.41745583628658245</v>
       </c>
-      <c r="J65" s="17">
+      <c r="J65" s="15">
         <f t="shared" si="2"/>
         <v>33010.836534861046</v>
       </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" s="2"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A66" s="85">
+      <c r="A66" s="78">
         <v>44460</v>
       </c>
-      <c r="B66" s="13">
+      <c r="B66" s="11">
         <v>44461</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D66" s="16" t="s">
+      <c r="D66" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="14">
         <v>50</v>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="14">
         <v>60</v>
       </c>
-      <c r="G66" s="16">
+      <c r="G66" s="14">
         <v>375</v>
       </c>
-      <c r="H66" s="16">
+      <c r="H66" s="14">
         <v>4011223</v>
       </c>
-      <c r="I66" s="16">
+      <c r="I66" s="14">
         <f t="shared" si="1"/>
         <v>-0.31592012975692418</v>
       </c>
-      <c r="J66" s="17">
+      <c r="J66" s="15">
         <f t="shared" si="2"/>
         <v>32105.666515061155</v>
       </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" s="2"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24844,1238 +24817,1237 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="96" t="s">
+      <c r="C1" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="97" t="s">
+      <c r="D1" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="98" t="s">
+      <c r="E1" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="98" t="s">
+      <c r="F1" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="98" t="s">
+      <c r="G1" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="98" t="s">
+      <c r="H1" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="99"/>
-      <c r="J1" s="100" t="s">
+      <c r="I1" s="90"/>
+      <c r="J1" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="100" t="s">
+      <c r="K1" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="100" t="s">
+      <c r="L1" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="100" t="s">
+      <c r="M1" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="100" t="s">
+      <c r="N1" s="91" t="s">
         <v>41</v>
       </c>
-      <c r="O1" s="101" t="s">
+      <c r="O1" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="135" t="s">
+      <c r="P1" s="125" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="93">
+      <c r="C2" s="57">
         <v>10</v>
       </c>
-      <c r="D2" s="94">
+      <c r="D2" s="4">
         <f>('STDs and Samples'!I7)</f>
         <v>0.48855508351652155</v>
       </c>
-      <c r="E2" s="94">
+      <c r="E2" s="4">
         <f>('STDs and Samples'!J7)</f>
         <v>3415.3455195636461</v>
       </c>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5">
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4">
         <f>AVERAGE(D2:D6)</f>
         <v>0.4686384641587808</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <f>STDEV(D2:D6)</f>
         <v>0.22796415588288529</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <f>K2/SQRT(5)</f>
         <v>0.10194866979749802</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="4">
         <f>AVERAGE(E2:E6)</f>
         <v>3826.5337522628774</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="4">
         <f>STDEV(E2:E6)</f>
         <v>1045.722121169721</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="7">
         <f>N2/SQRT(5)</f>
         <v>467.66114970215364</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="14">
         <v>10</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="5">
         <f>('STDs and Samples'!I11)</f>
         <v>0.7248208621720722</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="5">
         <f>('STDs and Samples'!J11)</f>
         <v>4206.4111027123072</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="81"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="9"/>
     </row>
     <row r="4" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="14">
         <v>10</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="5">
         <f>('STDs and Samples'!I15)</f>
         <v>0.51198640040798105</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="5">
         <f>('STDs and Samples'!J15)</f>
         <v>4418.2986371472098</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="10"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="9"/>
     </row>
     <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="14">
         <v>10</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="14">
         <f>('STDs and Samples'!I19)</f>
         <v>9.8033135325528376E-2</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="14">
         <f>('STDs and Samples'!J19)</f>
         <v>4879.2576936294181</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="10"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="9"/>
     </row>
     <row r="6" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="33">
         <v>10</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="33">
         <f>('STDs and Samples'!I23)</f>
         <v>0.51979683937180088</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="33">
         <f>('STDs and Samples'!J23)</f>
         <v>2213.3558082618092</v>
       </c>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="112"/>
-      <c r="L6" s="112"/>
-      <c r="M6" s="112"/>
-      <c r="N6" s="112"/>
-      <c r="O6" s="113"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="103"/>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="116" t="s">
+      <c r="A7" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="117" t="s">
+      <c r="B7" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="117">
+      <c r="C7" s="107">
         <v>20</v>
       </c>
-      <c r="D7" s="118">
+      <c r="D7" s="108">
         <f>('STDs and Samples'!I8)</f>
         <v>-0.15580613099861707</v>
       </c>
-      <c r="E7" s="118">
+      <c r="E7" s="108">
         <f>('STDs and Samples'!J8)</f>
         <v>7093.065739137005</v>
       </c>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118">
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108">
         <f>AVERAGE(D7:D11)</f>
         <v>-0.19602989166228935</v>
       </c>
-      <c r="K7" s="118">
+      <c r="K7" s="108">
         <f>STDEV(D7:D11)</f>
         <v>0.20135847132331361</v>
       </c>
-      <c r="L7" s="118">
+      <c r="L7" s="108">
         <f>K7/SQRT(5)</f>
         <v>9.0050245944874249E-2</v>
       </c>
-      <c r="M7" s="118">
+      <c r="M7" s="108">
         <f>AVERAGE(E7:E11)</f>
         <v>11613.050784741708</v>
       </c>
-      <c r="N7" s="118">
+      <c r="N7" s="108">
         <f>STDEV(E7:E11)</f>
         <v>3556.8801397717225</v>
       </c>
-      <c r="O7" s="119">
+      <c r="O7" s="109">
         <f>N7/SQRT(5)</f>
         <v>1590.6851560697048</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="102" t="s">
+      <c r="A8" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="103" t="s">
+      <c r="B8" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="103">
+      <c r="C8" s="94">
         <v>20</v>
       </c>
-      <c r="D8" s="104">
+      <c r="D8" s="95">
         <f>('STDs and Samples'!I12)</f>
         <v>0.11951184247603308</v>
       </c>
-      <c r="E8" s="104">
+      <c r="E8" s="95">
         <f>('STDs and Samples'!J12)</f>
         <v>16738.614671304331</v>
       </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="104"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="104"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="104"/>
-      <c r="O8" s="105"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="95"/>
+      <c r="K8" s="95"/>
+      <c r="L8" s="95"/>
+      <c r="M8" s="95"/>
+      <c r="N8" s="95"/>
+      <c r="O8" s="96"/>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="102" t="s">
+      <c r="A9" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="103">
+      <c r="C9" s="94">
         <v>20</v>
       </c>
-      <c r="D9" s="104">
+      <c r="D9" s="95">
         <f>('STDs and Samples'!I16)</f>
         <v>-0.23195791089586071</v>
       </c>
-      <c r="E9" s="104">
+      <c r="E9" s="95">
         <f>('STDs and Samples'!J16)</f>
         <v>12917.279552845132</v>
       </c>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="104"/>
-      <c r="K9" s="104"/>
-      <c r="L9" s="104"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="104"/>
-      <c r="O9" s="105"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="95"/>
+      <c r="K9" s="95"/>
+      <c r="L9" s="95"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="95"/>
+      <c r="O9" s="96"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="102" t="s">
+      <c r="A10" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="103" t="s">
+      <c r="B10" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="103">
+      <c r="C10" s="94">
         <v>20</v>
       </c>
-      <c r="D10" s="103">
+      <c r="D10" s="94">
         <f>('STDs and Samples'!I20)</f>
         <v>-0.29053620312450967</v>
       </c>
-      <c r="E10" s="103">
+      <c r="E10" s="94">
         <f>('STDs and Samples'!J20)</f>
         <v>11093.589350520939</v>
       </c>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="104"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="104"/>
-      <c r="O10" s="105"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="95"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="95"/>
+      <c r="L10" s="95"/>
+      <c r="M10" s="95"/>
+      <c r="N10" s="95"/>
+      <c r="O10" s="96"/>
     </row>
     <row r="11" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="107" t="s">
+      <c r="A11" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="108" t="s">
+      <c r="B11" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="108">
+      <c r="C11" s="99">
         <v>20</v>
       </c>
-      <c r="D11" s="108">
+      <c r="D11" s="99">
         <f>('STDs and Samples'!I24)</f>
         <v>-0.42136105576849237</v>
       </c>
-      <c r="E11" s="108">
+      <c r="E11" s="99">
         <f>('STDs and Samples'!J24)</f>
         <v>10222.704609901131</v>
       </c>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="109"/>
-      <c r="J11" s="109"/>
-      <c r="K11" s="109"/>
-      <c r="L11" s="109"/>
-      <c r="M11" s="109"/>
-      <c r="N11" s="109"/>
-      <c r="O11" s="110"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="100"/>
+      <c r="O11" s="101"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="92" t="s">
+      <c r="A12" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="93" t="s">
+      <c r="B12" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="93">
+      <c r="C12" s="57">
         <v>35</v>
       </c>
-      <c r="D12" s="94">
+      <c r="D12" s="4">
         <f>('STDs and Samples'!I9)</f>
         <v>-0.30615708105214945</v>
       </c>
-      <c r="E12" s="94">
+      <c r="E12" s="4">
         <f>('STDs and Samples'!J9)</f>
         <v>9601.0604826538511</v>
       </c>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5">
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4">
         <f>AVERAGE(D12:D16)</f>
         <v>-0.19368675997314339</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="4">
         <f>STDEV(D12:D16)</f>
         <v>0.20260431477963156</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="4">
         <f>K12/SQRT(5)</f>
         <v>9.0607404076404288E-2</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="4">
         <f>AVERAGE(E12:E16)</f>
         <v>17350.80256748795</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="4">
         <f>STDEV(E12:E16)</f>
         <v>11105.652799179683</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="7">
         <f>N12/SQRT(5)</f>
         <v>4966.5989186953184</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="14">
         <v>35</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="5">
         <f>('STDs and Samples'!I13)</f>
         <v>3.9454843096879522E-2</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="5">
         <f>('STDs and Samples'!J13)</f>
         <v>36113.219494393474</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="10"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="9"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="90" t="s">
+      <c r="A14" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="14">
         <v>35</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="5">
         <f>('STDs and Samples'!I17)</f>
         <v>-0.11675393617951779</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="5">
         <f>('STDs and Samples'!J17)</f>
         <v>10110.621217184664</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="10"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="9"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="14">
         <v>35</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="14">
         <f>('STDs and Samples'!I21)</f>
         <v>-0.10308566799283303</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="14">
         <f>('STDs and Samples'!J21)</f>
         <v>12169.163166302045</v>
       </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="10"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="9"/>
     </row>
     <row r="16" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="111" t="s">
+      <c r="A16" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="33">
         <v>35</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="33">
         <f>('STDs and Samples'!I25)</f>
         <v>-0.48189195773809623</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="33">
         <f>('STDs and Samples'!J25)</f>
         <v>18759.948476905709</v>
       </c>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="112"/>
-      <c r="J16" s="112"/>
-      <c r="K16" s="112"/>
-      <c r="L16" s="112"/>
-      <c r="M16" s="112"/>
-      <c r="N16" s="112"/>
-      <c r="O16" s="113"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="103"/>
     </row>
     <row r="17" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="116" t="s">
+      <c r="A17" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="117" t="s">
+      <c r="B17" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="117">
+      <c r="C17" s="107">
         <v>50</v>
       </c>
-      <c r="D17" s="118">
+      <c r="D17" s="108">
         <f>('STDs and Samples'!I10)</f>
         <v>-0.3178727394978792</v>
       </c>
-      <c r="E17" s="118">
+      <c r="E17" s="108">
         <f>('STDs and Samples'!J10)</f>
         <v>16734.814142470841</v>
       </c>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="118"/>
-      <c r="J17" s="118">
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="108">
         <f>AVERAGE(D17:D21)</f>
         <v>-0.33310309547732792</v>
       </c>
-      <c r="K17" s="118">
+      <c r="K17" s="108">
         <f>STDEV(D17:D21)</f>
         <v>7.6119229444849404E-2</v>
       </c>
-      <c r="L17" s="118">
+      <c r="L17" s="108">
         <f>K17/SQRT(5)</f>
         <v>3.4041554286717367E-2</v>
       </c>
-      <c r="M17" s="118">
+      <c r="M17" s="108">
         <f>AVERAGE(E17:E21)</f>
         <v>17235.095789231076</v>
       </c>
-      <c r="N17" s="118">
+      <c r="N17" s="108">
         <f>STDEV(E17:E21)</f>
         <v>3739.5468676564078</v>
       </c>
-      <c r="O17" s="119">
+      <c r="O17" s="109">
         <f>N17/SQRT(5)</f>
         <v>1672.3762002252274</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="102" t="s">
+      <c r="A18" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="103">
+      <c r="C18" s="94">
         <v>50</v>
       </c>
-      <c r="D18" s="104">
+      <c r="D18" s="95">
         <f>('STDs and Samples'!I14)</f>
         <v>-0.30029925182928452</v>
       </c>
-      <c r="E18" s="104">
+      <c r="E18" s="95">
         <f>('STDs and Samples'!J14)</f>
         <v>22888.280974251458</v>
       </c>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="104"/>
-      <c r="N18" s="104"/>
-      <c r="O18" s="105"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="95"/>
+      <c r="K18" s="95"/>
+      <c r="L18" s="95"/>
+      <c r="M18" s="95"/>
+      <c r="N18" s="95"/>
+      <c r="O18" s="96"/>
     </row>
     <row r="19" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="102" t="s">
+      <c r="A19" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="103" t="s">
+      <c r="B19" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="103">
+      <c r="C19" s="94">
         <v>50</v>
       </c>
-      <c r="D19" s="104">
+      <c r="D19" s="95">
         <f>('STDs and Samples'!I18)</f>
         <v>-0.26710488623305007</v>
       </c>
-      <c r="E19" s="104">
+      <c r="E19" s="95">
         <f>('STDs and Samples'!J18)</f>
         <v>15221.382366019559</v>
       </c>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="104"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="104"/>
-      <c r="K19" s="104"/>
-      <c r="L19" s="104"/>
-      <c r="M19" s="104"/>
-      <c r="N19" s="104"/>
-      <c r="O19" s="105"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="95"/>
+      <c r="K19" s="95"/>
+      <c r="L19" s="95"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="95"/>
+      <c r="O19" s="96"/>
     </row>
     <row r="20" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="102" t="s">
+      <c r="A20" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="103" t="s">
+      <c r="B20" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="103">
+      <c r="C20" s="94">
         <v>50</v>
       </c>
-      <c r="D20" s="103">
+      <c r="D20" s="94">
         <f>('STDs and Samples'!I22)</f>
         <v>-0.31592012975692418</v>
       </c>
-      <c r="E20" s="103">
+      <c r="E20" s="94">
         <f>('STDs and Samples'!J22)</f>
         <v>12950.195997487725</v>
       </c>
-      <c r="F20" s="103"/>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="104"/>
-      <c r="O20" s="105"/>
+      <c r="F20" s="94"/>
+      <c r="G20" s="94"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="95"/>
+      <c r="L20" s="95"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="95"/>
+      <c r="O20" s="96"/>
     </row>
     <row r="21" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="107" t="s">
+      <c r="A21" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="108" t="s">
+      <c r="B21" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="108">
+      <c r="C21" s="99">
         <v>50</v>
       </c>
-      <c r="D21" s="108">
+      <c r="D21" s="99">
         <f>('STDs and Samples'!I26)</f>
         <v>-0.46431847006950155</v>
       </c>
-      <c r="E21" s="108">
+      <c r="E21" s="99">
         <f>('STDs and Samples'!J26)</f>
         <v>18380.805465925801</v>
       </c>
-      <c r="F21" s="108"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="108"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="110"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="99"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="100"/>
+      <c r="N21" s="100"/>
+      <c r="O21" s="101"/>
     </row>
     <row r="22" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="115" t="s">
+      <c r="A22" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="93">
+      <c r="C22" s="57">
         <v>10</v>
       </c>
-      <c r="D22" s="93">
+      <c r="D22" s="57">
         <f>('STDs and Samples'!I27)</f>
         <v>0.10974879377125824</v>
       </c>
-      <c r="E22" s="93">
+      <c r="E22" s="57">
         <f>('STDs and Samples'!J27)</f>
         <v>6195.4404132290238</v>
       </c>
-      <c r="F22" s="93"/>
-      <c r="G22" s="93"/>
-      <c r="H22" s="93"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5">
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4">
         <f>AVERAGE(D22:D26)</f>
         <v>0.44559766921551225</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22" s="4">
         <f>STDEV(D22:D26)</f>
         <v>0.25575833667605363</v>
       </c>
-      <c r="L22" s="5">
+      <c r="L22" s="4">
         <f>K22/SQRT(5)</f>
         <v>0.11437860532398671</v>
       </c>
-      <c r="M22" s="5">
+      <c r="M22" s="4">
         <f>AVERAGE(E22:E26)</f>
         <v>6338.3435181553732</v>
       </c>
-      <c r="N22" s="5">
+      <c r="N22" s="4">
         <f>STDEV(E22:E26)</f>
         <v>1596.5621845265116</v>
       </c>
-      <c r="O22" s="8">
+      <c r="O22" s="7">
         <f>N22/SQRT(5)</f>
         <v>714.00431498136857</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="91" t="s">
+      <c r="A23" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="14">
         <v>10</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="5">
         <f>('STDs and Samples'!I31)</f>
         <v>0.45536071792028698</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="5">
         <f>('STDs and Samples'!J31)</f>
         <v>6642.7111243363761</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="10"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="9"/>
     </row>
     <row r="24" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="14">
         <v>10</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="5">
         <f>('STDs and Samples'!I35)</f>
         <v>0.82830917844268548</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="5">
         <f>('STDs and Samples'!J35)</f>
         <v>4384.9071264004288</v>
       </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="10"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="9"/>
     </row>
     <row r="25" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="91" t="s">
+      <c r="A25" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="14">
         <v>10</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="5">
         <f>('STDs and Samples'!I39)</f>
         <v>0.39873503543259314</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="5">
         <f>('STDs and Samples'!J39)</f>
         <v>8761.0067269989377</v>
       </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="10"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="9"/>
     </row>
     <row r="26" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="114" t="s">
+      <c r="A26" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="33">
         <v>10</v>
       </c>
-      <c r="D26" s="46">
+      <c r="D26" s="44">
         <f>('STDs and Samples'!I43)</f>
         <v>0.43583462051073729</v>
       </c>
-      <c r="E26" s="46">
+      <c r="E26" s="44">
         <f>('STDs and Samples'!J43)</f>
         <v>5707.6521998120979</v>
       </c>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="112"/>
-      <c r="K26" s="112"/>
-      <c r="L26" s="112"/>
-      <c r="M26" s="112"/>
-      <c r="N26" s="112"/>
-      <c r="O26" s="113"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="103"/>
     </row>
     <row r="27" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="120" t="s">
+      <c r="A27" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="117" t="s">
+      <c r="B27" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="117">
+      <c r="C27" s="107">
         <v>20</v>
       </c>
-      <c r="D27" s="117">
+      <c r="D27" s="107">
         <f>('STDs and Samples'!I28)</f>
         <v>-0.33544622716647388</v>
       </c>
-      <c r="E27" s="117">
+      <c r="E27" s="107">
         <f>('STDs and Samples'!J28)</f>
         <v>12291.730221182079</v>
       </c>
-      <c r="F27" s="117"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="117"/>
-      <c r="I27" s="118"/>
-      <c r="J27" s="118">
+      <c r="F27" s="107"/>
+      <c r="G27" s="107"/>
+      <c r="H27" s="107"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="108">
         <f>AVERAGE(D27:D31)</f>
         <v>-0.11519184838675378</v>
       </c>
-      <c r="K27" s="118">
+      <c r="K27" s="108">
         <f>STDEV(D27:D31)</f>
         <v>0.13658082926703299</v>
       </c>
-      <c r="L27" s="118">
+      <c r="L27" s="108">
         <f>K27/SQRT(5)</f>
         <v>6.1080803732875708E-2</v>
       </c>
-      <c r="M27" s="118">
+      <c r="M27" s="108">
         <f>AVERAGE(E27:E31)</f>
         <v>11531.473077488286</v>
       </c>
-      <c r="N27" s="118">
+      <c r="N27" s="108">
         <f>STDEV(E27:E31)</f>
         <v>1931.3120710300477</v>
       </c>
-      <c r="O27" s="119">
+      <c r="O27" s="109">
         <f>N27/SQRT(5)</f>
         <v>863.70901531781772</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="103" t="s">
+      <c r="B28" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="103">
+      <c r="C28" s="94">
         <v>20</v>
       </c>
-      <c r="D28" s="104">
+      <c r="D28" s="95">
         <f>('STDs and Samples'!I32)</f>
         <v>-0.13432742384811247</v>
       </c>
-      <c r="E28" s="104">
+      <c r="E28" s="95">
         <f>('STDs and Samples'!J32)</f>
         <v>13771.722175079372</v>
       </c>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="104"/>
-      <c r="N28" s="104"/>
-      <c r="O28" s="105"/>
+      <c r="F28" s="95"/>
+      <c r="G28" s="95"/>
+      <c r="H28" s="95"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="95"/>
+      <c r="K28" s="95"/>
+      <c r="L28" s="95"/>
+      <c r="M28" s="95"/>
+      <c r="N28" s="95"/>
+      <c r="O28" s="96"/>
     </row>
     <row r="29" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="106" t="s">
+      <c r="A29" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="103" t="s">
+      <c r="B29" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="103">
+      <c r="C29" s="94">
         <v>20</v>
       </c>
-      <c r="D29" s="104">
+      <c r="D29" s="95">
         <f>('STDs and Samples'!I36)</f>
         <v>-9.3322619288058184E-2</v>
       </c>
-      <c r="E29" s="104">
+      <c r="E29" s="95">
         <f>('STDs and Samples'!J36)</f>
         <v>9447.6382869053159</v>
       </c>
-      <c r="F29" s="104"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="104"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="104"/>
-      <c r="N29" s="104"/>
-      <c r="O29" s="105"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="95"/>
+      <c r="H29" s="95"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="95"/>
+      <c r="M29" s="95"/>
+      <c r="N29" s="95"/>
+      <c r="O29" s="96"/>
     </row>
     <row r="30" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="106" t="s">
+      <c r="A30" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="103" t="s">
+      <c r="B30" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="103">
+      <c r="C30" s="94">
         <v>20</v>
       </c>
-      <c r="D30" s="104">
+      <c r="D30" s="95">
         <f>('STDs and Samples'!I40)</f>
         <v>-3.4744327059409219E-2</v>
       </c>
-      <c r="E30" s="104">
+      <c r="E30" s="95">
         <f>('STDs and Samples'!J40)</f>
         <v>12583.211457987836</v>
       </c>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="104"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="104"/>
-      <c r="N30" s="104"/>
-      <c r="O30" s="105"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="95"/>
+      <c r="N30" s="95"/>
+      <c r="O30" s="96"/>
     </row>
     <row r="31" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="121" t="s">
+      <c r="A31" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="108" t="s">
+      <c r="B31" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="108">
+      <c r="C31" s="99">
         <v>20</v>
       </c>
-      <c r="D31" s="109">
+      <c r="D31" s="100">
         <f>('STDs and Samples'!I44)</f>
         <v>2.1881355428284843E-2</v>
       </c>
-      <c r="E31" s="109">
+      <c r="E31" s="100">
         <f>('STDs and Samples'!J44)</f>
         <v>9563.0632462868234</v>
       </c>
-      <c r="F31" s="109"/>
-      <c r="G31" s="109"/>
-      <c r="H31" s="109"/>
-      <c r="I31" s="109"/>
-      <c r="J31" s="109"/>
-      <c r="K31" s="109"/>
-      <c r="L31" s="109"/>
-      <c r="M31" s="109"/>
-      <c r="N31" s="109"/>
-      <c r="O31" s="110"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="100"/>
+      <c r="I31" s="100"/>
+      <c r="J31" s="100"/>
+      <c r="K31" s="100"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="100"/>
+      <c r="N31" s="100"/>
+      <c r="O31" s="101"/>
     </row>
     <row r="32" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="115" t="s">
+      <c r="A32" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="93" t="s">
+      <c r="B32" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="93">
+      <c r="C32" s="57">
         <v>35</v>
       </c>
-      <c r="D32" s="93">
+      <c r="D32" s="57">
         <f>('STDs and Samples'!I29)</f>
         <v>-1.9123449131769554E-2</v>
       </c>
-      <c r="E32" s="93">
+      <c r="E32" s="57">
         <f>('STDs and Samples'!J29)</f>
         <v>13574.650261520786</v>
       </c>
-      <c r="F32" s="93"/>
-      <c r="G32" s="93"/>
-      <c r="H32" s="93"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5">
+      <c r="F32" s="57"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4">
         <f>AVERAGE(D32:D36)</f>
         <v>-0.27140062766315098</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K32" s="4">
         <f>STDEV(D32:D36)</f>
         <v>0.2492213961100706</v>
       </c>
-      <c r="L32" s="5">
+      <c r="L32" s="4">
         <f>K32/SQRT(5)</f>
         <v>0.1114551966299039</v>
       </c>
-      <c r="M32" s="5">
+      <c r="M32" s="4">
         <f>AVERAGE(E32:E36)</f>
         <v>16241.79698112072</v>
       </c>
-      <c r="N32" s="5">
+      <c r="N32" s="4">
         <f>STDEV(E32:E36)</f>
         <v>4721.7062037424257</v>
       </c>
-      <c r="O32" s="8">
+      <c r="O32" s="7">
         <f>N32/SQRT(5)</f>
         <v>2111.611208270107</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A33" s="91" t="s">
+      <c r="A33" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="14">
         <v>35</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="5">
         <f>('STDs and Samples'!I33)</f>
         <v>-0.61271681038207892</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="5">
         <f>('STDs and Samples'!J33)</f>
         <v>24576.810843950749</v>
       </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="10"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="9"/>
     </row>
     <row r="34" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A34" s="91" t="s">
+      <c r="A34" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="14">
         <v>35</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="5">
         <f>('STDs and Samples'!I37)</f>
         <v>-0.4076927875818076</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="5">
         <f>('STDs and Samples'!J37)</f>
         <v>15436.853026155528</v>
       </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="10"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="9"/>
     </row>
     <row r="35" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A35" s="91" t="s">
+      <c r="A35" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="14">
         <v>35</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="5">
         <f>('STDs and Samples'!I41)</f>
         <v>-4.8412595246093981E-2</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="5">
         <f>('STDs and Samples'!J41)</f>
         <v>14055.248067631979</v>
       </c>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="10"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="9"/>
     </row>
     <row r="36" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="114" t="s">
+      <c r="A36" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="35" t="s">
+      <c r="B36" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="33">
         <v>35</v>
       </c>
-      <c r="D36" s="46">
+      <c r="D36" s="44">
         <f>('STDs and Samples'!I45)</f>
         <v>-0.26905749597400508</v>
       </c>
-      <c r="E36" s="46">
+      <c r="E36" s="44">
         <f>('STDs and Samples'!J45)</f>
         <v>13565.422706344558</v>
       </c>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="112"/>
-      <c r="J36" s="112"/>
-      <c r="K36" s="112"/>
-      <c r="L36" s="112"/>
-      <c r="M36" s="112"/>
-      <c r="N36" s="112"/>
-      <c r="O36" s="113"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="44"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="44"/>
+      <c r="N36" s="44"/>
+      <c r="O36" s="103"/>
     </row>
     <row r="37" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A37" s="120" t="s">
+      <c r="A37" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="117" t="s">
+      <c r="B37" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="117">
+      <c r="C37" s="107">
         <v>50</v>
       </c>
-      <c r="D37" s="117">
+      <c r="D37" s="107">
         <f>('STDs and Samples'!I30)</f>
         <v>-0.33349361742551886</v>
       </c>
-      <c r="E37" s="117">
+      <c r="E37" s="107">
         <f>('STDs and Samples'!J30)</f>
         <v>25094.520169963536</v>
       </c>
-      <c r="F37" s="117"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="117"/>
-      <c r="I37" s="118"/>
-      <c r="J37" s="118">
+      <c r="F37" s="107"/>
+      <c r="G37" s="107"/>
+      <c r="H37" s="107"/>
+      <c r="I37" s="108"/>
+      <c r="J37" s="108">
         <f>AVERAGE(D37:D41)</f>
         <v>-0.35075711280147859</v>
       </c>
-      <c r="K37" s="118">
+      <c r="K37" s="108">
         <f>STDEV(D37:D41)</f>
         <v>0.23140831214452884</v>
       </c>
-      <c r="L37" s="118">
+      <c r="L37" s="108">
         <f>K37/SQRT(5)</f>
         <v>0.10348894330273133</v>
       </c>
-      <c r="M37" s="118">
+      <c r="M37" s="108">
         <f>AVERAGE(E37:E41)</f>
         <v>25887.648667279867</v>
       </c>
-      <c r="N37" s="118">
+      <c r="N37" s="108">
         <f>STDEV(E37:E41)</f>
         <v>4504.5233896735053</v>
       </c>
-      <c r="O37" s="119">
+      <c r="O37" s="109">
         <f>N37/SQRT(5)</f>
         <v>2014.4841011095464</v>
       </c>
@@ -26084,782 +26056,782 @@
       </c>
     </row>
     <row r="38" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A38" s="106" t="s">
+      <c r="A38" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="103" t="s">
+      <c r="B38" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="103">
+      <c r="C38" s="94">
         <v>50</v>
       </c>
-      <c r="D38" s="104">
+      <c r="D38" s="95">
         <f>('STDs and Samples'!I34)</f>
         <v>0</v>
       </c>
-      <c r="E38" s="104">
+      <c r="E38" s="95">
         <f>('STDs and Samples'!J34)</f>
         <v>33425.923530401749</v>
       </c>
-      <c r="F38" s="104"/>
-      <c r="G38" s="104"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="104"/>
-      <c r="N38" s="104"/>
-      <c r="O38" s="105"/>
+      <c r="F38" s="95"/>
+      <c r="G38" s="95"/>
+      <c r="H38" s="95"/>
+      <c r="I38" s="95"/>
+      <c r="J38" s="95"/>
+      <c r="K38" s="95"/>
+      <c r="L38" s="95"/>
+      <c r="M38" s="95"/>
+      <c r="N38" s="95"/>
+      <c r="O38" s="96"/>
     </row>
     <row r="39" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A39" s="106" t="s">
+      <c r="A39" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="103" t="s">
+      <c r="B39" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="103">
+      <c r="C39" s="94">
         <v>50</v>
       </c>
-      <c r="D39" s="104">
+      <c r="D39" s="95">
         <f>('STDs and Samples'!I38)</f>
         <v>-0.5404702499667452</v>
       </c>
-      <c r="E39" s="104">
+      <c r="E39" s="95">
         <f>('STDs and Samples'!J38)</f>
         <v>25749.724899282817</v>
       </c>
-      <c r="F39" s="104"/>
-      <c r="G39" s="104"/>
-      <c r="H39" s="104"/>
-      <c r="I39" s="104"/>
-      <c r="J39" s="104"/>
-      <c r="K39" s="104"/>
-      <c r="L39" s="104"/>
-      <c r="M39" s="104"/>
-      <c r="N39" s="104"/>
-      <c r="O39" s="105"/>
+      <c r="F39" s="95"/>
+      <c r="G39" s="95"/>
+      <c r="H39" s="95"/>
+      <c r="I39" s="95"/>
+      <c r="J39" s="95"/>
+      <c r="K39" s="95"/>
+      <c r="L39" s="95"/>
+      <c r="M39" s="95"/>
+      <c r="N39" s="95"/>
+      <c r="O39" s="96"/>
     </row>
     <row r="40" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A40" s="106" t="s">
+      <c r="A40" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="103" t="s">
+      <c r="B40" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="103">
+      <c r="C40" s="94">
         <v>50</v>
       </c>
-      <c r="D40" s="104">
+      <c r="D40" s="95">
         <f>('STDs and Samples'!I42)</f>
         <v>-0.30029925182928452</v>
       </c>
-      <c r="E40" s="104">
+      <c r="E40" s="95">
         <f>('STDs and Samples'!J42)</f>
         <v>21619.266682420031</v>
       </c>
-      <c r="F40" s="104"/>
-      <c r="G40" s="104"/>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="104"/>
-      <c r="K40" s="104"/>
-      <c r="L40" s="104"/>
-      <c r="M40" s="104"/>
-      <c r="N40" s="104"/>
-      <c r="O40" s="105"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="95"/>
+      <c r="J40" s="95"/>
+      <c r="K40" s="95"/>
+      <c r="L40" s="95"/>
+      <c r="M40" s="95"/>
+      <c r="N40" s="95"/>
+      <c r="O40" s="96"/>
     </row>
     <row r="41" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="121" t="s">
+      <c r="A41" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="108" t="s">
+      <c r="B41" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="108">
+      <c r="C41" s="99">
         <v>50</v>
       </c>
-      <c r="D41" s="109">
+      <c r="D41" s="100">
         <f>('STDs and Samples'!I46)</f>
         <v>-0.57952244478584447</v>
       </c>
-      <c r="E41" s="109">
+      <c r="E41" s="100">
         <f>('STDs and Samples'!J46)</f>
         <v>23548.808054331199</v>
       </c>
-      <c r="F41" s="109"/>
-      <c r="G41" s="109"/>
-      <c r="H41" s="109"/>
-      <c r="I41" s="109"/>
-      <c r="J41" s="109"/>
-      <c r="K41" s="109"/>
-      <c r="L41" s="109"/>
-      <c r="M41" s="109"/>
-      <c r="N41" s="109"/>
-      <c r="O41" s="110"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="100"/>
+      <c r="J41" s="100"/>
+      <c r="K41" s="100"/>
+      <c r="L41" s="100"/>
+      <c r="M41" s="100"/>
+      <c r="N41" s="100"/>
+      <c r="O41" s="101"/>
     </row>
     <row r="42" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A42" s="92" t="s">
+      <c r="A42" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="93" t="s">
+      <c r="B42" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="93">
+      <c r="C42" s="57">
         <v>10</v>
       </c>
-      <c r="D42" s="94">
+      <c r="D42" s="4">
         <f>('STDs and Samples'!I47)</f>
         <v>0.68576866735297304</v>
       </c>
-      <c r="E42" s="94">
+      <c r="E42" s="4">
         <f>('STDs and Samples'!J47)</f>
         <v>3397.5265146727311</v>
       </c>
-      <c r="F42" s="94"/>
-      <c r="G42" s="94"/>
-      <c r="H42" s="94"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5">
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4">
         <f>AVERAGE(D42:D46)</f>
         <v>0.40381182075907596</v>
       </c>
-      <c r="K42" s="5">
+      <c r="K42" s="4">
         <f>STDEV(D42:D46)</f>
         <v>0.18083316896158771</v>
       </c>
-      <c r="L42" s="5">
+      <c r="L42" s="4">
         <f>K42/SQRT(5)</f>
         <v>8.0871051676963027E-2</v>
       </c>
-      <c r="M42" s="5">
+      <c r="M42" s="4">
         <f>AVERAGE(E42:E46)</f>
         <v>7445.8916983385716</v>
       </c>
-      <c r="N42" s="5">
+      <c r="N42" s="4">
         <f>STDEV(E42:E46)</f>
         <v>3219.0944878815135</v>
       </c>
-      <c r="O42" s="8">
+      <c r="O42" s="7">
         <f>N42/SQRT(5)</f>
         <v>1439.6228201795873</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A43" s="90" t="s">
+      <c r="A43" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="14">
         <v>10</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="5">
         <f>('STDs and Samples'!I51)</f>
         <v>0.37335110880017841</v>
       </c>
-      <c r="E43" s="12">
+      <c r="E43" s="5">
         <f>('STDs and Samples'!J51)</f>
         <v>9136.8564831210133</v>
       </c>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="10"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="9"/>
     </row>
     <row r="44" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A44" s="90" t="s">
+      <c r="A44" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="14">
         <v>10</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="5">
         <f>('STDs and Samples'!I55)</f>
         <v>0.29524671916197986</v>
       </c>
-      <c r="E44" s="12">
+      <c r="E44" s="5">
         <f>('STDs and Samples'!J55)</f>
         <v>8603.4780276379497</v>
       </c>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="10"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="9"/>
     </row>
     <row r="45" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A45" s="90" t="s">
+      <c r="A45" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="14">
         <v>10</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="5">
         <f>('STDs and Samples'!I59)</f>
         <v>0.45145549843837718</v>
       </c>
-      <c r="E45" s="12">
+      <c r="E45" s="5">
         <f>('STDs and Samples'!J59)</f>
         <v>4872.3249492954474</v>
       </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="10"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="9"/>
     </row>
     <row r="46" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="111" t="s">
+      <c r="A46" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="35">
+      <c r="C46" s="33">
         <v>10</v>
       </c>
-      <c r="D46" s="46">
+      <c r="D46" s="44">
         <f>('STDs and Samples'!I63)</f>
         <v>0.21323711004187129</v>
       </c>
-      <c r="E46" s="46">
+      <c r="E46" s="44">
         <f>('STDs and Samples'!J63)</f>
         <v>11219.272516965717</v>
       </c>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="46"/>
-      <c r="I46" s="112"/>
-      <c r="J46" s="112"/>
-      <c r="K46" s="112"/>
-      <c r="L46" s="112"/>
-      <c r="M46" s="112"/>
-      <c r="N46" s="112"/>
-      <c r="O46" s="113"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="44"/>
+      <c r="M46" s="44"/>
+      <c r="N46" s="44"/>
+      <c r="O46" s="103"/>
     </row>
     <row r="47" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="B47" s="117" t="s">
+      <c r="B47" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="117">
+      <c r="C47" s="107">
         <v>20</v>
       </c>
-      <c r="D47" s="118">
+      <c r="D47" s="108">
         <f>('STDs and Samples'!I48)</f>
         <v>-0.14994830177575214</v>
       </c>
-      <c r="E47" s="118">
+      <c r="E47" s="108">
         <f>('STDs and Samples'!J48)</f>
         <v>13196.690889817412</v>
       </c>
-      <c r="F47" s="118"/>
-      <c r="G47" s="118"/>
-      <c r="H47" s="118"/>
-      <c r="I47" s="118"/>
-      <c r="J47" s="118">
+      <c r="F47" s="108"/>
+      <c r="G47" s="108"/>
+      <c r="H47" s="108"/>
+      <c r="I47" s="108"/>
+      <c r="J47" s="108">
         <f>AVERAGE(D47:D51)</f>
         <v>-0.24289252544520851</v>
       </c>
-      <c r="K47" s="118">
+      <c r="K47" s="108">
         <f>STDEV(D47:D51)</f>
         <v>6.7309830993704994E-2</v>
       </c>
-      <c r="L47" s="118">
+      <c r="L47" s="108">
         <f>K47/SQRT(5)</f>
         <v>3.0101871531189317E-2</v>
       </c>
-      <c r="M47" s="118">
+      <c r="M47" s="108">
         <f>AVERAGE(E47:E51)</f>
         <v>17247.001428920055</v>
       </c>
-      <c r="N47" s="118">
+      <c r="N47" s="108">
         <f>STDEV(E47:E51)</f>
         <v>4781.2678724510897</v>
       </c>
-      <c r="O47" s="119">
+      <c r="O47" s="109">
         <f>N47/SQRT(5)</f>
         <v>2138.2479962872862</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A48" s="102" t="s">
+      <c r="A48" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="B48" s="103" t="s">
+      <c r="B48" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="103">
+      <c r="C48" s="94">
         <v>20</v>
       </c>
-      <c r="D48" s="104">
+      <c r="D48" s="95">
         <f>('STDs and Samples'!I52)</f>
         <v>-0.20071615504058127</v>
       </c>
-      <c r="E48" s="104">
+      <c r="E48" s="95">
         <f>('STDs and Samples'!J52)</f>
         <v>19418.929579154876</v>
       </c>
-      <c r="F48" s="104"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="104"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="104"/>
-      <c r="K48" s="104"/>
-      <c r="L48" s="104"/>
-      <c r="M48" s="104"/>
-      <c r="N48" s="104"/>
-      <c r="O48" s="105"/>
+      <c r="F48" s="95"/>
+      <c r="G48" s="95"/>
+      <c r="H48" s="95"/>
+      <c r="I48" s="95"/>
+      <c r="J48" s="95"/>
+      <c r="K48" s="95"/>
+      <c r="L48" s="95"/>
+      <c r="M48" s="95"/>
+      <c r="N48" s="95"/>
+      <c r="O48" s="96"/>
     </row>
     <row r="49" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A49" s="102" t="s">
+      <c r="A49" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="103" t="s">
+      <c r="B49" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="103">
+      <c r="C49" s="94">
         <v>20</v>
       </c>
-      <c r="D49" s="104">
+      <c r="D49" s="95">
         <f>('STDs and Samples'!I56)</f>
         <v>-0.25538922778732032</v>
       </c>
-      <c r="E49" s="104">
+      <c r="E49" s="95">
         <f>('STDs and Samples'!J56)</f>
         <v>23520.811362055683</v>
       </c>
-      <c r="F49" s="104"/>
-      <c r="G49" s="104"/>
-      <c r="H49" s="104"/>
-      <c r="I49" s="104"/>
-      <c r="J49" s="104"/>
-      <c r="K49" s="104"/>
-      <c r="L49" s="104"/>
-      <c r="M49" s="104"/>
-      <c r="N49" s="104"/>
-      <c r="O49" s="105"/>
+      <c r="F49" s="95"/>
+      <c r="G49" s="95"/>
+      <c r="H49" s="95"/>
+      <c r="I49" s="95"/>
+      <c r="J49" s="95"/>
+      <c r="K49" s="95"/>
+      <c r="L49" s="95"/>
+      <c r="M49" s="95"/>
+      <c r="N49" s="95"/>
+      <c r="O49" s="96"/>
     </row>
     <row r="50" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A50" s="102" t="s">
+      <c r="A50" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="B50" s="103" t="s">
+      <c r="B50" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C50" s="103">
+      <c r="C50" s="94">
         <v>20</v>
       </c>
-      <c r="D50" s="104">
+      <c r="D50" s="95">
         <f>('STDs and Samples'!I60)</f>
         <v>-0.30029925182928452</v>
       </c>
-      <c r="E50" s="104">
+      <c r="E50" s="95">
         <f>('STDs and Samples'!J60)</f>
         <v>11785.913651709681</v>
       </c>
-      <c r="F50" s="104"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="104"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="104"/>
-      <c r="K50" s="104"/>
-      <c r="L50" s="104"/>
-      <c r="M50" s="104"/>
-      <c r="N50" s="104"/>
-      <c r="O50" s="105"/>
+      <c r="F50" s="95"/>
+      <c r="G50" s="95"/>
+      <c r="H50" s="95"/>
+      <c r="I50" s="95"/>
+      <c r="J50" s="95"/>
+      <c r="K50" s="95"/>
+      <c r="L50" s="95"/>
+      <c r="M50" s="95"/>
+      <c r="N50" s="95"/>
+      <c r="O50" s="96"/>
     </row>
     <row r="51" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="107" t="s">
+      <c r="A51" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="108" t="s">
+      <c r="B51" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="108">
+      <c r="C51" s="99">
         <v>20</v>
       </c>
-      <c r="D51" s="109">
+      <c r="D51" s="100">
         <f>('STDs and Samples'!I64)</f>
         <v>-0.30810969079310435</v>
       </c>
-      <c r="E51" s="109">
+      <c r="E51" s="100">
         <f>('STDs and Samples'!J64)</f>
         <v>18312.661661862621</v>
       </c>
-      <c r="F51" s="109"/>
-      <c r="G51" s="109"/>
-      <c r="H51" s="109"/>
-      <c r="I51" s="109"/>
-      <c r="J51" s="109"/>
-      <c r="K51" s="109"/>
-      <c r="L51" s="109"/>
-      <c r="M51" s="109"/>
-      <c r="N51" s="109"/>
-      <c r="O51" s="110"/>
+      <c r="F51" s="100"/>
+      <c r="G51" s="100"/>
+      <c r="H51" s="100"/>
+      <c r="I51" s="100"/>
+      <c r="J51" s="100"/>
+      <c r="K51" s="100"/>
+      <c r="L51" s="100"/>
+      <c r="M51" s="100"/>
+      <c r="N51" s="100"/>
+      <c r="O51" s="101"/>
     </row>
     <row r="52" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A52" s="92" t="s">
+      <c r="A52" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B52" s="93" t="s">
+      <c r="B52" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="93">
+      <c r="C52" s="57">
         <v>35</v>
       </c>
-      <c r="D52" s="94">
+      <c r="D52" s="4">
         <f>('STDs and Samples'!I49)</f>
         <v>-0.14409047255288732</v>
       </c>
-      <c r="E52" s="94">
+      <c r="E52" s="4">
         <f>('STDs and Samples'!J49)</f>
         <v>17249.503980533293</v>
       </c>
-      <c r="F52" s="94"/>
-      <c r="G52" s="94"/>
-      <c r="H52" s="94"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5">
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4">
         <f>AVERAGE(D52:D56)</f>
         <v>-0.19251519412857043</v>
       </c>
-      <c r="K52" s="5">
+      <c r="K52" s="4">
         <f>STDEV(D52:D56)</f>
         <v>0.21247319105466314</v>
       </c>
-      <c r="L52" s="5">
+      <c r="L52" s="4">
         <f>K52/SQRT(5)</f>
         <v>9.5020899718905399E-2</v>
       </c>
-      <c r="M52" s="5">
+      <c r="M52" s="4">
         <f>AVERAGE(E52:E56)</f>
         <v>21203.942959024018</v>
       </c>
-      <c r="N52" s="5">
+      <c r="N52" s="4">
         <f>STDEV(E52:E56)</f>
         <v>7165.3056472582011</v>
       </c>
-      <c r="O52" s="8">
+      <c r="O52" s="7">
         <f>N52/SQRT(5)</f>
         <v>3204.4221013664933</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A53" s="90" t="s">
+      <c r="A53" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="14">
         <v>35</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="5">
         <f>('STDs and Samples'!I53)</f>
         <v>-0.13237481410715746</v>
       </c>
-      <c r="E53" s="12">
+      <c r="E53" s="5">
         <f>('STDs and Samples'!J53)</f>
         <v>22768.70119945029</v>
       </c>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="10"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="9"/>
     </row>
     <row r="54" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A54" s="90" t="s">
+      <c r="A54" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="14">
         <v>35</v>
       </c>
-      <c r="D54" s="12">
+      <c r="D54" s="5">
         <f>('STDs and Samples'!I57)</f>
         <v>0.10779618403030322</v>
       </c>
-      <c r="E54" s="12">
+      <c r="E54" s="5">
         <f>('STDs and Samples'!J57)</f>
         <v>17824.937864188636</v>
       </c>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="10"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="9"/>
     </row>
     <row r="55" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A55" s="90" t="s">
+      <c r="A55" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="14">
         <v>35</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="5">
         <f>('STDs and Samples'!I61)</f>
         <v>-0.37645103172652816</v>
       </c>
-      <c r="E55" s="12">
+      <c r="E55" s="5">
         <f>('STDs and Samples'!J61)</f>
         <v>15165.735216086836</v>
       </c>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="10"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="9"/>
     </row>
     <row r="56" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="111" t="s">
+      <c r="A56" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="B56" s="35" t="s">
+      <c r="B56" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C56" s="35">
+      <c r="C56" s="33">
         <v>35</v>
       </c>
-      <c r="D56" s="46">
+      <c r="D56" s="44">
         <f>('STDs and Samples'!I65)</f>
         <v>-0.41745583628658245</v>
       </c>
-      <c r="E56" s="46">
+      <c r="E56" s="44">
         <f>('STDs and Samples'!J65)</f>
         <v>33010.836534861046</v>
       </c>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="112"/>
-      <c r="J56" s="112"/>
-      <c r="K56" s="112"/>
-      <c r="L56" s="112"/>
-      <c r="M56" s="112"/>
-      <c r="N56" s="112"/>
-      <c r="O56" s="113"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="44"/>
+      <c r="J56" s="44"/>
+      <c r="K56" s="44"/>
+      <c r="L56" s="44"/>
+      <c r="M56" s="44"/>
+      <c r="N56" s="44"/>
+      <c r="O56" s="103"/>
     </row>
     <row r="57" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A57" s="116" t="s">
+      <c r="A57" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="B57" s="117" t="s">
+      <c r="B57" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="117">
+      <c r="C57" s="107">
         <v>50</v>
       </c>
-      <c r="D57" s="118">
+      <c r="D57" s="108">
         <f>('STDs and Samples'!I50)</f>
         <v>-0.45455542136472671</v>
       </c>
-      <c r="E57" s="118">
+      <c r="E57" s="108">
         <f>('STDs and Samples'!J50)</f>
         <v>33407.65361531025</v>
       </c>
-      <c r="F57" s="118"/>
-      <c r="G57" s="118"/>
-      <c r="H57" s="118"/>
-      <c r="I57" s="118"/>
-      <c r="J57" s="118">
+      <c r="F57" s="108"/>
+      <c r="G57" s="108"/>
+      <c r="H57" s="108"/>
+      <c r="I57" s="108"/>
+      <c r="J57" s="108">
         <f>AVERAGE(D57:D61)</f>
         <v>-0.31748221754968819</v>
       </c>
-      <c r="K57" s="118">
+      <c r="K57" s="108">
         <f>STDEV(D57:D61)</f>
         <v>8.6879065945110565E-2</v>
       </c>
-      <c r="L57" s="118">
+      <c r="L57" s="108">
         <f>K57/SQRT(5)</f>
         <v>3.8853499454990843E-2</v>
       </c>
-      <c r="M57" s="118">
+      <c r="M57" s="108">
         <f>AVERAGE(E57:E61)</f>
         <v>28165.624455117631</v>
       </c>
-      <c r="N57" s="118">
+      <c r="N57" s="108">
         <f>STDEV(E57:E61)</f>
         <v>7916.8876537096066</v>
       </c>
-      <c r="O57" s="119">
+      <c r="O57" s="109">
         <f>N57/SQRT(5)</f>
         <v>3540.5397927846989</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A58" s="102" t="s">
+      <c r="A58" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="B58" s="103" t="s">
+      <c r="B58" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="103">
+      <c r="C58" s="94">
         <v>50</v>
       </c>
-      <c r="D58" s="104">
+      <c r="D58" s="95">
         <f>('STDs and Samples'!I54)</f>
         <v>-0.26319966675114015</v>
       </c>
-      <c r="E58" s="104">
+      <c r="E58" s="95">
         <f>('STDs and Samples'!J54)</f>
         <v>19712.641211059949</v>
       </c>
-      <c r="F58" s="104"/>
-      <c r="G58" s="104"/>
-      <c r="H58" s="104"/>
-      <c r="I58" s="104"/>
-      <c r="J58" s="104"/>
-      <c r="K58" s="104"/>
-      <c r="L58" s="104"/>
-      <c r="M58" s="104"/>
-      <c r="N58" s="104"/>
-      <c r="O58" s="105"/>
+      <c r="F58" s="95"/>
+      <c r="G58" s="95"/>
+      <c r="H58" s="95"/>
+      <c r="I58" s="95"/>
+      <c r="J58" s="95"/>
+      <c r="K58" s="95"/>
+      <c r="L58" s="95"/>
+      <c r="M58" s="95"/>
+      <c r="N58" s="95"/>
+      <c r="O58" s="96"/>
     </row>
     <row r="59" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A59" s="102" t="s">
+      <c r="A59" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="B59" s="103" t="s">
+      <c r="B59" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="103">
+      <c r="C59" s="94">
         <v>50</v>
       </c>
-      <c r="D59" s="104">
+      <c r="D59" s="95">
         <f>('STDs and Samples'!I58)</f>
         <v>-0.22610008167299578</v>
       </c>
-      <c r="E59" s="104">
+      <c r="E59" s="95">
         <f>('STDs and Samples'!J58)</f>
         <v>36046.895435068356</v>
       </c>
-      <c r="F59" s="104"/>
-      <c r="G59" s="104"/>
-      <c r="H59" s="104"/>
-      <c r="I59" s="104"/>
-      <c r="J59" s="104"/>
-      <c r="K59" s="104"/>
-      <c r="L59" s="104"/>
-      <c r="M59" s="104"/>
-      <c r="N59" s="104"/>
-      <c r="O59" s="105"/>
+      <c r="F59" s="95"/>
+      <c r="G59" s="95"/>
+      <c r="H59" s="95"/>
+      <c r="I59" s="95"/>
+      <c r="J59" s="95"/>
+      <c r="K59" s="95"/>
+      <c r="L59" s="95"/>
+      <c r="M59" s="95"/>
+      <c r="N59" s="95"/>
+      <c r="O59" s="96"/>
     </row>
     <row r="60" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A60" s="102" t="s">
+      <c r="A60" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="B60" s="103" t="s">
+      <c r="B60" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C60" s="103">
+      <c r="C60" s="94">
         <v>50</v>
       </c>
-      <c r="D60" s="104">
+      <c r="D60" s="95">
         <f>('STDs and Samples'!I62)</f>
         <v>-0.32763578820265404</v>
       </c>
-      <c r="E60" s="104">
+      <c r="E60" s="95">
         <f>('STDs and Samples'!J62)</f>
         <v>19555.265499088444</v>
       </c>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="104"/>
-      <c r="L60" s="104"/>
-      <c r="M60" s="104"/>
-      <c r="N60" s="104"/>
-      <c r="O60" s="105"/>
+      <c r="F60" s="95"/>
+      <c r="G60" s="95"/>
+      <c r="H60" s="95"/>
+      <c r="I60" s="95"/>
+      <c r="J60" s="95"/>
+      <c r="K60" s="95"/>
+      <c r="L60" s="95"/>
+      <c r="M60" s="95"/>
+      <c r="N60" s="95"/>
+      <c r="O60" s="96"/>
     </row>
     <row r="61" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="107" t="s">
+      <c r="A61" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="B61" s="108" t="s">
+      <c r="B61" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C61" s="108">
+      <c r="C61" s="99">
         <v>50</v>
       </c>
-      <c r="D61" s="109">
+      <c r="D61" s="100">
         <f>('STDs and Samples'!I66)</f>
         <v>-0.31592012975692418</v>
       </c>
-      <c r="E61" s="109">
+      <c r="E61" s="100">
         <f>('STDs and Samples'!J66)</f>
         <v>32105.666515061155</v>
       </c>
-      <c r="F61" s="109"/>
-      <c r="G61" s="109"/>
-      <c r="H61" s="109"/>
-      <c r="I61" s="109"/>
-      <c r="J61" s="109"/>
-      <c r="K61" s="109"/>
-      <c r="L61" s="109"/>
-      <c r="M61" s="109"/>
-      <c r="N61" s="109"/>
-      <c r="O61" s="110"/>
+      <c r="F61" s="100"/>
+      <c r="G61" s="100"/>
+      <c r="H61" s="100"/>
+      <c r="I61" s="100"/>
+      <c r="J61" s="100"/>
+      <c r="K61" s="100"/>
+      <c r="L61" s="100"/>
+      <c r="M61" s="100"/>
+      <c r="N61" s="100"/>
+      <c r="O61" s="101"/>
     </row>
     <row r="62" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A62" s="79"/>
-      <c r="B62" s="79"/>
-      <c r="C62" s="79"/>
-      <c r="D62" s="79"/>
-      <c r="E62" s="79"/>
-      <c r="F62" s="79"/>
-      <c r="G62" s="79"/>
-      <c r="H62" s="79"/>
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S62">
